--- a/results/block1_results/Normal_2/branches/dataframes/dataset_LCA_B07_Normal_2.xlsx
+++ b/results/block1_results/Normal_2/branches/dataframes/dataset_LCA_B07_Normal_2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I288"/>
+  <dimension ref="A1:J282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,6 +474,11 @@
           <t>PointType</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Segment_ID</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -493,21 +498,24 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>208.0319366455078</v>
+        <v>189.0160675048828</v>
       </c>
       <c r="F2" t="n">
-        <v>263.7550964355469</v>
+        <v>291.7065124511719</v>
       </c>
       <c r="G2" t="n">
-        <v>-93.68702697753906</v>
+        <v>-84.40533447265625</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6467354252878443</v>
+        <v>0.3601162941928505</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>Ostium</t>
         </is>
+      </c>
+      <c r="J2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -528,21 +536,24 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>208.0002288818359</v>
+        <v>189.3370361328125</v>
       </c>
       <c r="F3" t="n">
-        <v>263.8824157714844</v>
+        <v>291.6298828125</v>
       </c>
       <c r="G3" t="n">
-        <v>-93.05374145507812</v>
+        <v>-84.54952239990234</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6467354252878443</v>
+        <v>0.3601162941928505</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J3" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -563,21 +574,24 @@
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>207.9902954101562</v>
+        <v>189.4462280273438</v>
       </c>
       <c r="F4" t="n">
-        <v>263.8923034667969</v>
+        <v>291.5890197753906</v>
       </c>
       <c r="G4" t="n">
-        <v>-93.03369140625</v>
+        <v>-84.59609222412109</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6629988028460425</v>
+        <v>0.4102223282871231</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J4" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -598,21 +612,24 @@
         <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>207.9892578125</v>
+        <v>189.9311065673828</v>
       </c>
       <c r="F5" t="n">
-        <v>263.9239807128906</v>
+        <v>291.4532165527344</v>
       </c>
       <c r="G5" t="n">
-        <v>-93.01251983642578</v>
+        <v>-84.49253082275391</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6690004658526879</v>
+        <v>0.5825333394926286</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J5" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -633,21 +650,24 @@
         <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>208.0671539306641</v>
+        <v>189.9691314697266</v>
       </c>
       <c r="F6" t="n">
-        <v>264.1255187988281</v>
+        <v>291.4439086914062</v>
       </c>
       <c r="G6" t="n">
-        <v>-92.83025360107422</v>
+        <v>-84.50959014892578</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6429185698242229</v>
+        <v>0.6019010630345635</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J6" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -668,21 +688,24 @@
         <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>208.0720825195312</v>
+        <v>190.3195953369141</v>
       </c>
       <c r="F7" t="n">
-        <v>264.1333923339844</v>
+        <v>291.3957214355469</v>
       </c>
       <c r="G7" t="n">
-        <v>-92.824462890625</v>
+        <v>-84.492919921875</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6431247973115828</v>
+        <v>0.7198397021314636</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -703,21 +726,24 @@
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>208.1506500244141</v>
+        <v>190.3831481933594</v>
       </c>
       <c r="F8" t="n">
-        <v>264.2560424804688</v>
+        <v>291.409912109375</v>
       </c>
       <c r="G8" t="n">
-        <v>-92.74085998535156</v>
+        <v>-84.48550415039062</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6476115651411589</v>
+        <v>0.7423713894432257</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -738,21 +764,24 @@
         <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>208.163818359375</v>
+        <v>190.8936614990234</v>
       </c>
       <c r="F9" t="n">
-        <v>264.2703552246094</v>
+        <v>291.4073791503906</v>
       </c>
       <c r="G9" t="n">
-        <v>-92.73365783691406</v>
+        <v>-84.37062072753906</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6472178938828617</v>
+        <v>0.9843276862778777</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J9" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -773,21 +802,24 @@
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>208.2371978759766</v>
+        <v>190.9704437255859</v>
       </c>
       <c r="F10" t="n">
-        <v>264.4110412597656</v>
+        <v>291.4301147460938</v>
       </c>
       <c r="G10" t="n">
-        <v>-92.64492797851562</v>
+        <v>-84.36591339111328</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6264078258650405</v>
+        <v>1.02661539854811</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J10" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -808,21 +840,24 @@
         <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>208.3054046630859</v>
+        <v>190.9826812744141</v>
       </c>
       <c r="F11" t="n">
-        <v>264.5780639648438</v>
+        <v>291.4347534179688</v>
       </c>
       <c r="G11" t="n">
-        <v>-92.51220703125</v>
+        <v>-84.36473083496094</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6220037227330554</v>
+        <v>1.033294950116688</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J11" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -843,21 +878,24 @@
         <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>208.350341796875</v>
+        <v>191.2830047607422</v>
       </c>
       <c r="F12" t="n">
-        <v>264.6416015625</v>
+        <v>291.3337097167969</v>
       </c>
       <c r="G12" t="n">
-        <v>-92.46891021728516</v>
+        <v>-84.45069885253906</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6275594972344394</v>
+        <v>1.01929601935633</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J12" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -878,21 +916,24 @@
         <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>208.4190063476562</v>
+        <v>191.2884063720703</v>
       </c>
       <c r="F13" t="n">
-        <v>264.8024291992188</v>
+        <v>291.3337097167969</v>
       </c>
       <c r="G13" t="n">
-        <v>-92.35890960693359</v>
+        <v>-84.4527587890625</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6503067890861475</v>
+        <v>1.019790706423236</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J13" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -913,21 +954,24 @@
         <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>208.4193572998047</v>
+        <v>191.35498046875</v>
       </c>
       <c r="F14" t="n">
-        <v>264.8047790527344</v>
+        <v>291.3245544433594</v>
       </c>
       <c r="G14" t="n">
-        <v>-92.35696411132812</v>
+        <v>-84.46717071533203</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6504412229973316</v>
+        <v>1.024555794042266</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -948,21 +992,24 @@
         <v>13</v>
       </c>
       <c r="E15" t="n">
-        <v>208.4193572998047</v>
+        <v>191.5795593261719</v>
       </c>
       <c r="F15" t="n">
-        <v>264.8048095703125</v>
+        <v>291.2610778808594</v>
       </c>
       <c r="G15" t="n">
-        <v>-92.35694122314453</v>
+        <v>-84.54829406738281</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6504428557978723</v>
+        <v>1.030223622333066</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J15" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -983,21 +1030,24 @@
         <v>14</v>
       </c>
       <c r="E16" t="n">
-        <v>208.5124206542969</v>
+        <v>191.7392730712891</v>
       </c>
       <c r="F16" t="n">
-        <v>265.0127258300781</v>
+        <v>291.2088623046875</v>
       </c>
       <c r="G16" t="n">
-        <v>-92.21111297607422</v>
+        <v>-84.57435607910156</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6645159398338392</v>
+        <v>1.05048239959312</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J16" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -1018,21 +1068,24 @@
         <v>15</v>
       </c>
       <c r="E17" t="n">
-        <v>208.5410308837891</v>
+        <v>192.1652221679688</v>
       </c>
       <c r="F17" t="n">
-        <v>265.0799560546875</v>
+        <v>291.0989685058594</v>
       </c>
       <c r="G17" t="n">
-        <v>-92.16258239746094</v>
+        <v>-84.59026336669922</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6823304231338193</v>
+        <v>1.143917691635046</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J17" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -1053,21 +1106,24 @@
         <v>16</v>
       </c>
       <c r="E18" t="n">
-        <v>208.56201171875</v>
+        <v>192.791748046875</v>
       </c>
       <c r="F18" t="n">
-        <v>265.1450500488281</v>
+        <v>290.9992065429688</v>
       </c>
       <c r="G18" t="n">
-        <v>-92.11402893066406</v>
+        <v>-84.56982421875</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6813728387149349</v>
+        <v>1.374902942689236</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J18" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -1088,21 +1144,24 @@
         <v>17</v>
       </c>
       <c r="E19" t="n">
-        <v>208.5660858154297</v>
+        <v>192.8433990478516</v>
       </c>
       <c r="F19" t="n">
-        <v>265.1544799804688</v>
+        <v>290.9930725097656</v>
       </c>
       <c r="G19" t="n">
-        <v>-92.1053466796875</v>
+        <v>-84.55848693847656</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6808891056158085</v>
+        <v>1.396731665571797</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J19" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1123,21 +1182,24 @@
         <v>18</v>
       </c>
       <c r="E20" t="n">
-        <v>208.5661010742188</v>
+        <v>193.4530181884766</v>
       </c>
       <c r="F20" t="n">
-        <v>265.1545104980469</v>
+        <v>290.7755737304688</v>
       </c>
       <c r="G20" t="n">
-        <v>-92.10530853271484</v>
+        <v>-84.39375305175781</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6808871629125992</v>
+        <v>1.675479405129489</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J20" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -1158,21 +1220,24 @@
         <v>19</v>
       </c>
       <c r="E21" t="n">
-        <v>208.6824798583984</v>
+        <v>193.4673461914062</v>
       </c>
       <c r="F21" t="n">
-        <v>265.3249816894531</v>
+        <v>290.7735595703125</v>
       </c>
       <c r="G21" t="n">
-        <v>-91.90596008300781</v>
+        <v>-84.38986206054688</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6922928261966714</v>
+        <v>1.683516892751304</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J21" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -1193,21 +1258,24 @@
         <v>20</v>
       </c>
       <c r="E22" t="n">
-        <v>208.6889190673828</v>
+        <v>193.5866241455078</v>
       </c>
       <c r="F22" t="n">
-        <v>265.3486022949219</v>
+        <v>290.7679748535156</v>
       </c>
       <c r="G22" t="n">
-        <v>-91.88065338134766</v>
+        <v>-84.35820007324219</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6923086577354375</v>
+        <v>1.753123654791975</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J22" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -1228,21 +1296,24 @@
         <v>21</v>
       </c>
       <c r="E23" t="n">
-        <v>208.7801055908203</v>
+        <v>193.8734893798828</v>
       </c>
       <c r="F23" t="n">
-        <v>265.4933166503906</v>
+        <v>290.624755859375</v>
       </c>
       <c r="G23" t="n">
-        <v>-91.68168640136719</v>
+        <v>-84.32112884521484</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6762613939077581</v>
+        <v>1.839291115181509</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J23" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -1263,21 +1334,24 @@
         <v>22</v>
       </c>
       <c r="E24" t="n">
-        <v>208.781982421875</v>
+        <v>193.8751831054688</v>
       </c>
       <c r="F24" t="n">
-        <v>265.5042724609375</v>
+        <v>290.6241760253906</v>
       </c>
       <c r="G24" t="n">
-        <v>-91.66901397705078</v>
+        <v>-84.32103729248047</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6743492038348713</v>
+        <v>1.839717991981493</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J24" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -1298,21 +1372,24 @@
         <v>23</v>
       </c>
       <c r="E25" t="n">
-        <v>208.7824401855469</v>
+        <v>193.9168701171875</v>
       </c>
       <c r="F25" t="n">
-        <v>265.6541748046875</v>
+        <v>290.6073303222656</v>
       </c>
       <c r="G25" t="n">
-        <v>-91.49250030517578</v>
+        <v>-84.32241058349609</v>
       </c>
       <c r="H25" t="n">
-        <v>0.670871246469246</v>
+        <v>1.846766556669689</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J25" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -1333,21 +1410,24 @@
         <v>24</v>
       </c>
       <c r="E26" t="n">
-        <v>208.8229827880859</v>
+        <v>194.0834655761719</v>
       </c>
       <c r="F26" t="n">
-        <v>265.7622985839844</v>
+        <v>290.5398864746094</v>
       </c>
       <c r="G26" t="n">
-        <v>-91.36436462402344</v>
+        <v>-84.29652404785156</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6779397610059809</v>
+        <v>1.876299476835571</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J26" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -1368,21 +1448,24 @@
         <v>25</v>
       </c>
       <c r="E27" t="n">
-        <v>208.8156433105469</v>
+        <v>194.4683685302734</v>
       </c>
       <c r="F27" t="n">
-        <v>265.8127136230469</v>
+        <v>290.4314575195312</v>
       </c>
       <c r="G27" t="n">
-        <v>-91.31111145019531</v>
+        <v>-84.20700073242188</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6695981555526757</v>
+        <v>1.953804889533968</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J27" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -1403,21 +1486,24 @@
         <v>26</v>
       </c>
       <c r="E28" t="n">
-        <v>208.8929443359375</v>
+        <v>194.6629943847656</v>
       </c>
       <c r="F28" t="n">
-        <v>266.1228332519531</v>
+        <v>290.4151306152344</v>
       </c>
       <c r="G28" t="n">
-        <v>-91.04353332519531</v>
+        <v>-84.20993804931641</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6797310391203149</v>
+        <v>1.960684200524002</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J28" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -1438,21 +1524,24 @@
         <v>27</v>
       </c>
       <c r="E29" t="n">
-        <v>208.9464263916016</v>
+        <v>194.8666076660156</v>
       </c>
       <c r="F29" t="n">
-        <v>266.2120666503906</v>
+        <v>290.4088745117188</v>
       </c>
       <c r="G29" t="n">
-        <v>-90.984619140625</v>
+        <v>-84.18038177490234</v>
       </c>
       <c r="H29" t="n">
-        <v>0.6789129081882471</v>
+        <v>1.976009104069842</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J29" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -1473,21 +1562,24 @@
         <v>28</v>
       </c>
       <c r="E30" t="n">
-        <v>208.9652862548828</v>
+        <v>194.9401092529297</v>
       </c>
       <c r="F30" t="n">
-        <v>266.2826232910156</v>
+        <v>290.4147033691406</v>
       </c>
       <c r="G30" t="n">
-        <v>-90.94176483154297</v>
+        <v>-84.17150115966797</v>
       </c>
       <c r="H30" t="n">
-        <v>0.6707473011301177</v>
+        <v>1.978342424100698</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J30" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -1508,21 +1600,24 @@
         <v>29</v>
       </c>
       <c r="E31" t="n">
-        <v>209.1060333251953</v>
+        <v>194.9779205322266</v>
       </c>
       <c r="F31" t="n">
-        <v>266.5542602539062</v>
+        <v>290.4086608886719</v>
       </c>
       <c r="G31" t="n">
-        <v>-90.66230010986328</v>
+        <v>-84.16666412353516</v>
       </c>
       <c r="H31" t="n">
-        <v>0.6934721651319258</v>
+        <v>1.975064733551531</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J31" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="32">
@@ -1543,21 +1638,24 @@
         <v>30</v>
       </c>
       <c r="E32" t="n">
-        <v>209.1067962646484</v>
+        <v>195.2982788085938</v>
       </c>
       <c r="F32" t="n">
-        <v>266.558349609375</v>
+        <v>290.3656616210938</v>
       </c>
       <c r="G32" t="n">
-        <v>-90.65982818603516</v>
+        <v>-84.14313507080078</v>
       </c>
       <c r="H32" t="n">
-        <v>0.6937953414022123</v>
+        <v>1.944107004163434</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J32" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="33">
@@ -1578,21 +1676,24 @@
         <v>31</v>
       </c>
       <c r="E33" t="n">
-        <v>209.2004852294922</v>
+        <v>195.3685607910156</v>
       </c>
       <c r="F33" t="n">
-        <v>266.7028198242188</v>
+        <v>290.3545227050781</v>
       </c>
       <c r="G33" t="n">
-        <v>-90.50820922851562</v>
+        <v>-84.15641021728516</v>
       </c>
       <c r="H33" t="n">
-        <v>0.6747661865001836</v>
+        <v>1.928573979575302</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J33" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="34">
@@ -1613,21 +1714,24 @@
         <v>32</v>
       </c>
       <c r="E34" t="n">
-        <v>209.2268829345703</v>
+        <v>195.3934173583984</v>
       </c>
       <c r="F34" t="n">
-        <v>266.9635314941406</v>
+        <v>290.3530883789062</v>
       </c>
       <c r="G34" t="n">
-        <v>-90.29446411132812</v>
+        <v>-84.16244506835938</v>
       </c>
       <c r="H34" t="n">
-        <v>0.6667968302355627</v>
+        <v>1.921593602400399</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J34" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="35">
@@ -1648,21 +1752,24 @@
         <v>33</v>
       </c>
       <c r="E35" t="n">
-        <v>209.3054046630859</v>
+        <v>195.4891967773438</v>
       </c>
       <c r="F35" t="n">
-        <v>267.082763671875</v>
+        <v>290.3360595703125</v>
       </c>
       <c r="G35" t="n">
-        <v>-90.20994567871094</v>
+        <v>-84.15049743652344</v>
       </c>
       <c r="H35" t="n">
-        <v>0.6667775671254508</v>
+        <v>1.917475223567121</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J35" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="36">
@@ -1683,21 +1790,24 @@
         <v>34</v>
       </c>
       <c r="E36" t="n">
-        <v>209.3059234619141</v>
+        <v>195.7372283935547</v>
       </c>
       <c r="F36" t="n">
-        <v>267.0846557617188</v>
+        <v>290.2706604003906</v>
       </c>
       <c r="G36" t="n">
-        <v>-90.20818328857422</v>
+        <v>-84.04450988769531</v>
       </c>
       <c r="H36" t="n">
-        <v>0.6667054830577938</v>
+        <v>1.976507154445902</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J36" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="37">
@@ -1718,21 +1828,24 @@
         <v>35</v>
       </c>
       <c r="E37" t="n">
-        <v>209.4167785644531</v>
+        <v>196.1260375976562</v>
       </c>
       <c r="F37" t="n">
-        <v>267.3092346191406</v>
+        <v>290.1980590820312</v>
       </c>
       <c r="G37" t="n">
-        <v>-89.98440551757812</v>
+        <v>-83.98835754394531</v>
       </c>
       <c r="H37" t="n">
-        <v>0.6621123461311131</v>
+        <v>2.021573580356052</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J37" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="38">
@@ -1753,21 +1866,24 @@
         <v>36</v>
       </c>
       <c r="E38" t="n">
-        <v>209.4302215576172</v>
+        <v>196.4047546386719</v>
       </c>
       <c r="F38" t="n">
-        <v>267.3848571777344</v>
+        <v>290.1246337890625</v>
       </c>
       <c r="G38" t="n">
-        <v>-89.92102813720703</v>
+        <v>-83.95450592041016</v>
       </c>
       <c r="H38" t="n">
-        <v>0.662062824057266</v>
+        <v>2.083124492630656</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J38" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="39">
@@ -1788,21 +1904,24 @@
         <v>37</v>
       </c>
       <c r="E39" t="n">
-        <v>209.491455078125</v>
+        <v>196.4092864990234</v>
       </c>
       <c r="F39" t="n">
-        <v>267.4644775390625</v>
+        <v>290.1234436035156</v>
       </c>
       <c r="G39" t="n">
-        <v>-89.80385589599609</v>
+        <v>-83.95395660400391</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6597087306228521</v>
+        <v>2.084125320472519</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J39" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="40">
@@ -1823,21 +1942,24 @@
         <v>38</v>
       </c>
       <c r="E40" t="n">
-        <v>209.5727844238281</v>
+        <v>196.4158325195312</v>
       </c>
       <c r="F40" t="n">
-        <v>267.676513671875</v>
+        <v>290.1213684082031</v>
       </c>
       <c r="G40" t="n">
-        <v>-89.52181243896484</v>
+        <v>-83.94772338867188</v>
       </c>
       <c r="H40" t="n">
-        <v>0.6936367770211276</v>
+        <v>2.089571330095493</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J40" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="41">
@@ -1858,21 +1980,24 @@
         <v>39</v>
       </c>
       <c r="E41" t="n">
-        <v>209.5971984863281</v>
+        <v>196.6074523925781</v>
       </c>
       <c r="F41" t="n">
-        <v>267.8004455566406</v>
+        <v>290.0853881835938</v>
       </c>
       <c r="G41" t="n">
-        <v>-89.39608001708984</v>
+        <v>-83.89820098876953</v>
       </c>
       <c r="H41" t="n">
-        <v>0.6952730895432755</v>
+        <v>2.145656269092434</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J41" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="42">
@@ -1893,21 +2018,24 @@
         <v>40</v>
       </c>
       <c r="E42" t="n">
-        <v>209.6894836425781</v>
+        <v>196.6547698974609</v>
       </c>
       <c r="F42" t="n">
-        <v>267.9549255371094</v>
+        <v>290.0728759765625</v>
       </c>
       <c r="G42" t="n">
-        <v>-89.24158477783203</v>
+        <v>-83.87587738037109</v>
       </c>
       <c r="H42" t="n">
-        <v>0.7116143980157031</v>
+        <v>2.166233443233783</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J42" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -1928,21 +2056,24 @@
         <v>41</v>
       </c>
       <c r="E43" t="n">
-        <v>209.7444610595703</v>
+        <v>196.8161773681641</v>
       </c>
       <c r="F43" t="n">
-        <v>268.180908203125</v>
+        <v>289.9920959472656</v>
       </c>
       <c r="G43" t="n">
-        <v>-89.03815460205078</v>
+        <v>-83.86679840087891</v>
       </c>
       <c r="H43" t="n">
-        <v>0.7682436258822795</v>
+        <v>2.175914843337889</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J43" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="44">
@@ -1963,21 +2094,24 @@
         <v>42</v>
       </c>
       <c r="E44" t="n">
-        <v>209.7537841796875</v>
+        <v>196.9035034179688</v>
       </c>
       <c r="F44" t="n">
-        <v>268.2157592773438</v>
+        <v>289.9342651367188</v>
       </c>
       <c r="G44" t="n">
-        <v>-88.99983978271484</v>
+        <v>-83.81912994384766</v>
       </c>
       <c r="H44" t="n">
-        <v>0.7764949284582445</v>
+        <v>2.197234617858366</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J44" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="45">
@@ -1998,21 +2132,24 @@
         <v>43</v>
       </c>
       <c r="E45" t="n">
-        <v>209.8257446289062</v>
+        <v>196.9193725585938</v>
       </c>
       <c r="F45" t="n">
-        <v>268.4435729980469</v>
+        <v>289.92431640625</v>
       </c>
       <c r="G45" t="n">
-        <v>-88.80947875976562</v>
+        <v>-83.81510925292969</v>
       </c>
       <c r="H45" t="n">
-        <v>0.7939926218633173</v>
+        <v>2.199052601485721</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J45" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="46">
@@ -2033,21 +2170,24 @@
         <v>44</v>
       </c>
       <c r="E46" t="n">
-        <v>209.8251037597656</v>
+        <v>196.9755859375</v>
       </c>
       <c r="F46" t="n">
-        <v>268.5283203125</v>
+        <v>289.8941040039062</v>
       </c>
       <c r="G46" t="n">
-        <v>-88.75107574462891</v>
+        <v>-83.80046844482422</v>
       </c>
       <c r="H46" t="n">
-        <v>0.7999982341247057</v>
+        <v>2.202001140902702</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J46" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="47">
@@ -2068,21 +2208,24 @@
         <v>45</v>
       </c>
       <c r="E47" t="n">
-        <v>209.8503723144531</v>
+        <v>197.2000427246094</v>
       </c>
       <c r="F47" t="n">
-        <v>268.6498718261719</v>
+        <v>289.8166198730469</v>
       </c>
       <c r="G47" t="n">
-        <v>-88.68128967285156</v>
+        <v>-83.74179077148438</v>
       </c>
       <c r="H47" t="n">
-        <v>0.8130369502643694</v>
+        <v>2.193484509194115</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J47" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="48">
@@ -2103,21 +2246,24 @@
         <v>46</v>
       </c>
       <c r="E48" t="n">
-        <v>209.8710174560547</v>
+        <v>197.3197174072266</v>
       </c>
       <c r="F48" t="n">
-        <v>268.7184753417969</v>
+        <v>289.7899169921875</v>
       </c>
       <c r="G48" t="n">
-        <v>-88.61603546142578</v>
+        <v>-83.71928405761719</v>
       </c>
       <c r="H48" t="n">
-        <v>0.8184166713327761</v>
+        <v>2.188208745117063</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J48" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="49">
@@ -2138,21 +2284,24 @@
         <v>47</v>
       </c>
       <c r="E49" t="n">
-        <v>209.8880310058594</v>
+        <v>197.4461517333984</v>
       </c>
       <c r="F49" t="n">
-        <v>268.74755859375</v>
+        <v>289.7622680664062</v>
       </c>
       <c r="G49" t="n">
-        <v>-88.59068298339844</v>
+        <v>-83.69757843017578</v>
       </c>
       <c r="H49" t="n">
-        <v>0.8195010799545517</v>
+        <v>2.18367115506424</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J49" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="50">
@@ -2173,21 +2322,24 @@
         <v>48</v>
       </c>
       <c r="E50" t="n">
-        <v>209.9079742431641</v>
+        <v>197.5771636962891</v>
       </c>
       <c r="F50" t="n">
-        <v>268.8198547363281</v>
+        <v>289.7228698730469</v>
       </c>
       <c r="G50" t="n">
-        <v>-88.51808166503906</v>
+        <v>-83.68088531494141</v>
       </c>
       <c r="H50" t="n">
-        <v>0.8199363651615775</v>
+        <v>2.178434919021832</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J50" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="51">
@@ -2208,21 +2360,24 @@
         <v>49</v>
       </c>
       <c r="E51" t="n">
-        <v>210.0212097167969</v>
+        <v>197.5878753662109</v>
       </c>
       <c r="F51" t="n">
-        <v>269.1904907226562</v>
+        <v>289.7196655273438</v>
       </c>
       <c r="G51" t="n">
-        <v>-88.2666015625</v>
+        <v>-83.67971038818359</v>
       </c>
       <c r="H51" t="n">
-        <v>0.8691589808172913</v>
+        <v>2.17813100543263</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J51" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="52">
@@ -2243,21 +2398,24 @@
         <v>50</v>
       </c>
       <c r="E52" t="n">
-        <v>210.0338134765625</v>
+        <v>198.0468139648438</v>
       </c>
       <c r="F52" t="n">
-        <v>269.2258605957031</v>
+        <v>289.6165161132812</v>
       </c>
       <c r="G52" t="n">
-        <v>-88.24948883056641</v>
+        <v>-83.60108947753906</v>
       </c>
       <c r="H52" t="n">
-        <v>0.8794977495855978</v>
+        <v>2.188018633795052</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J52" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="53">
@@ -2278,21 +2436,24 @@
         <v>51</v>
       </c>
       <c r="E53" t="n">
-        <v>210.2349395751953</v>
+        <v>198.0636138916016</v>
       </c>
       <c r="F53" t="n">
-        <v>269.561767578125</v>
+        <v>289.6132507324219</v>
       </c>
       <c r="G53" t="n">
-        <v>-87.90599060058594</v>
+        <v>-83.59816741943359</v>
       </c>
       <c r="H53" t="n">
-        <v>0.9618589145241625</v>
+        <v>2.189834571332291</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J53" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="54">
@@ -2313,21 +2474,24 @@
         <v>52</v>
       </c>
       <c r="E54" t="n">
-        <v>210.2829437255859</v>
+        <v>198.0636749267578</v>
       </c>
       <c r="F54" t="n">
-        <v>269.6587219238281</v>
+        <v>289.6132507324219</v>
       </c>
       <c r="G54" t="n">
-        <v>-87.82149505615234</v>
+        <v>-83.59815216064453</v>
       </c>
       <c r="H54" t="n">
-        <v>1.00491901882126</v>
+        <v>2.189841864254128</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J54" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="55">
@@ -2348,21 +2512,24 @@
         <v>53</v>
       </c>
       <c r="E55" t="n">
-        <v>210.4653472900391</v>
+        <v>198.21142578125</v>
       </c>
       <c r="F55" t="n">
-        <v>269.9132080078125</v>
+        <v>289.6017150878906</v>
       </c>
       <c r="G55" t="n">
-        <v>-87.39662933349609</v>
+        <v>-83.57537078857422</v>
       </c>
       <c r="H55" t="n">
-        <v>1.20088111406572</v>
+        <v>2.195061676834836</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J55" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="56">
@@ -2383,21 +2550,24 @@
         <v>54</v>
       </c>
       <c r="E56" t="n">
-        <v>210.4672698974609</v>
+        <v>198.4709777832031</v>
       </c>
       <c r="F56" t="n">
-        <v>269.9190673828125</v>
+        <v>289.5602416992188</v>
       </c>
       <c r="G56" t="n">
-        <v>-87.38774871826172</v>
+        <v>-83.55416107177734</v>
       </c>
       <c r="H56" t="n">
-        <v>1.205549772505801</v>
+        <v>2.204691290539358</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J56" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="57">
@@ -2418,21 +2588,24 @@
         <v>55</v>
       </c>
       <c r="E57" t="n">
-        <v>210.4693298339844</v>
+        <v>198.5215454101562</v>
       </c>
       <c r="F57" t="n">
-        <v>269.9371032714844</v>
+        <v>289.5528869628906</v>
       </c>
       <c r="G57" t="n">
-        <v>-87.37315368652344</v>
+        <v>-83.54952239990234</v>
       </c>
       <c r="H57" t="n">
-        <v>1.213680618503021</v>
+        <v>2.207526684182982</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J57" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="58">
@@ -2453,21 +2626,24 @@
         <v>56</v>
       </c>
       <c r="E58" t="n">
-        <v>210.4693450927734</v>
+        <v>198.5530395507812</v>
       </c>
       <c r="F58" t="n">
-        <v>269.9371643066406</v>
+        <v>289.5511474609375</v>
       </c>
       <c r="G58" t="n">
-        <v>-87.37309265136719</v>
+        <v>-83.54635620117188</v>
       </c>
       <c r="H58" t="n">
-        <v>1.213713272503009</v>
+        <v>2.208095004936173</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J58" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="59">
@@ -2488,21 +2664,24 @@
         <v>57</v>
       </c>
       <c r="E59" t="n">
-        <v>210.4701843261719</v>
+        <v>198.9823608398438</v>
       </c>
       <c r="F59" t="n">
-        <v>269.94287109375</v>
+        <v>289.493408203125</v>
       </c>
       <c r="G59" t="n">
-        <v>-87.36614227294922</v>
+        <v>-83.51004791259766</v>
       </c>
       <c r="H59" t="n">
-        <v>1.215774626652885</v>
+        <v>2.225949691807147</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J59" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="60">
@@ -2523,21 +2702,24 @@
         <v>58</v>
       </c>
       <c r="E60" t="n">
-        <v>210.4719085693359</v>
+        <v>198.9888610839844</v>
       </c>
       <c r="F60" t="n">
-        <v>269.9464721679688</v>
+        <v>289.4914245605469</v>
       </c>
       <c r="G60" t="n">
-        <v>-87.35830688476562</v>
+        <v>-83.50942993164062</v>
       </c>
       <c r="H60" t="n">
-        <v>1.216889776870386</v>
+        <v>2.225832291888918</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J60" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="61">
@@ -2558,21 +2740,24 @@
         <v>59</v>
       </c>
       <c r="E61" t="n">
-        <v>210.4719085693359</v>
+        <v>199.0043334960938</v>
       </c>
       <c r="F61" t="n">
-        <v>269.9464721679688</v>
+        <v>289.4859619140625</v>
       </c>
       <c r="G61" t="n">
-        <v>-87.3582763671875</v>
+        <v>-83.50885009765625</v>
       </c>
       <c r="H61" t="n">
-        <v>1.216894255385316</v>
+        <v>2.224916287126288</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J61" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="62">
@@ -2593,21 +2778,24 @@
         <v>60</v>
       </c>
       <c r="E62" t="n">
-        <v>210.4548187255859</v>
+        <v>199.2683715820312</v>
       </c>
       <c r="F62" t="n">
-        <v>270.0730895996094</v>
+        <v>289.4173889160156</v>
       </c>
       <c r="G62" t="n">
-        <v>-87.05564880371094</v>
+        <v>-83.541015625</v>
       </c>
       <c r="H62" t="n">
-        <v>1.238830602357058</v>
+        <v>2.208827057122309</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J62" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="63">
@@ -2628,21 +2816,24 @@
         <v>61</v>
       </c>
       <c r="E63" t="n">
-        <v>210.4469757080078</v>
+        <v>199.4115142822266</v>
       </c>
       <c r="F63" t="n">
-        <v>270.1963806152344</v>
+        <v>289.3599853515625</v>
       </c>
       <c r="G63" t="n">
-        <v>-86.88273620605469</v>
+        <v>-83.51624298095703</v>
       </c>
       <c r="H63" t="n">
-        <v>1.254744924174096</v>
+        <v>2.192679814598037</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J63" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="64">
@@ -2663,21 +2854,24 @@
         <v>62</v>
       </c>
       <c r="E64" t="n">
-        <v>210.4427032470703</v>
+        <v>200.1221313476562</v>
       </c>
       <c r="F64" t="n">
-        <v>270.2646484375</v>
+        <v>289.1310729980469</v>
       </c>
       <c r="G64" t="n">
-        <v>-86.72219085693359</v>
+        <v>-83.31981658935547</v>
       </c>
       <c r="H64" t="n">
-        <v>1.273058451156498</v>
+        <v>2.201579429588387</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J64" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="65">
@@ -2698,21 +2892,24 @@
         <v>63</v>
       </c>
       <c r="E65" t="n">
-        <v>210.4501190185547</v>
+        <v>200.1473388671875</v>
       </c>
       <c r="F65" t="n">
-        <v>270.4269409179688</v>
+        <v>289.1255493164062</v>
       </c>
       <c r="G65" t="n">
-        <v>-86.46763610839844</v>
+        <v>-83.31931304931641</v>
       </c>
       <c r="H65" t="n">
-        <v>1.313243232108084</v>
+        <v>2.202811552682574</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J65" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="66">
@@ -2733,21 +2930,24 @@
         <v>64</v>
       </c>
       <c r="E66" t="n">
-        <v>210.4476623535156</v>
+        <v>200.1871185302734</v>
       </c>
       <c r="F66" t="n">
-        <v>270.4727172851562</v>
+        <v>289.1162719726562</v>
       </c>
       <c r="G66" t="n">
-        <v>-86.42221832275391</v>
+        <v>-83.31841278076172</v>
       </c>
       <c r="H66" t="n">
-        <v>1.318132643251124</v>
+        <v>2.204572571517586</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J66" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="67">
@@ -2768,21 +2968,24 @@
         <v>65</v>
       </c>
       <c r="E67" t="n">
-        <v>210.4502868652344</v>
+        <v>200.2836761474609</v>
       </c>
       <c r="F67" t="n">
-        <v>270.5000305175781</v>
+        <v>289.0521850585938</v>
       </c>
       <c r="G67" t="n">
-        <v>-86.39653778076172</v>
+        <v>-83.31809234619141</v>
       </c>
       <c r="H67" t="n">
-        <v>1.320344280728808</v>
+        <v>2.192033070334196</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J67" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="68">
@@ -2803,21 +3006,24 @@
         <v>66</v>
       </c>
       <c r="E68" t="n">
-        <v>210.3987274169922</v>
+        <v>200.4189605712891</v>
       </c>
       <c r="F68" t="n">
-        <v>270.8297119140625</v>
+        <v>288.971923828125</v>
       </c>
       <c r="G68" t="n">
-        <v>-86.07470703125</v>
+        <v>-83.28870391845703</v>
       </c>
       <c r="H68" t="n">
-        <v>1.354860180519526</v>
+        <v>2.155245802111497</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J68" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="69">
@@ -2838,21 +3044,24 @@
         <v>67</v>
       </c>
       <c r="E69" t="n">
-        <v>210.4091796875</v>
+        <v>200.5168762207031</v>
       </c>
       <c r="F69" t="n">
-        <v>271.2772827148438</v>
+        <v>288.9258728027344</v>
       </c>
       <c r="G69" t="n">
-        <v>-85.76636505126953</v>
+        <v>-83.25727844238281</v>
       </c>
       <c r="H69" t="n">
-        <v>1.477601924949009</v>
+        <v>2.126686103342911</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J69" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="70">
@@ -2873,21 +3082,24 @@
         <v>68</v>
       </c>
       <c r="E70" t="n">
-        <v>210.396240234375</v>
+        <v>200.51806640625</v>
       </c>
       <c r="F70" t="n">
-        <v>271.3458251953125</v>
+        <v>288.9253234863281</v>
       </c>
       <c r="G70" t="n">
-        <v>-85.72745513916016</v>
+        <v>-83.25689697265625</v>
       </c>
       <c r="H70" t="n">
-        <v>1.498345449157989</v>
+        <v>2.1263392244105</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J70" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="71">
@@ -2908,21 +3120,24 @@
         <v>69</v>
       </c>
       <c r="E71" t="n">
-        <v>210.3037261962891</v>
+        <v>200.5506439208984</v>
       </c>
       <c r="F71" t="n">
-        <v>271.9171752929688</v>
+        <v>288.9078979492188</v>
       </c>
       <c r="G71" t="n">
-        <v>-85.58795928955078</v>
+        <v>-83.24209594726562</v>
       </c>
       <c r="H71" t="n">
-        <v>1.636648461877261</v>
+        <v>2.11368177283875</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J71" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="72">
@@ -2943,21 +3158,24 @@
         <v>70</v>
       </c>
       <c r="E72" t="n">
-        <v>210.3093566894531</v>
+        <v>200.5517272949219</v>
       </c>
       <c r="F72" t="n">
-        <v>272.0210571289062</v>
+        <v>288.9073181152344</v>
       </c>
       <c r="G72" t="n">
-        <v>-85.57356262207031</v>
+        <v>-83.24160766601562</v>
       </c>
       <c r="H72" t="n">
-        <v>1.663227255313188</v>
+        <v>2.113263344687618</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J72" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="73">
@@ -2978,21 +3196,24 @@
         <v>71</v>
       </c>
       <c r="E73" t="n">
-        <v>210.3281860351562</v>
+        <v>200.7511596679688</v>
       </c>
       <c r="F73" t="n">
-        <v>272.4547119140625</v>
+        <v>288.7605895996094</v>
       </c>
       <c r="G73" t="n">
-        <v>-85.54070281982422</v>
+        <v>-83.15990447998047</v>
       </c>
       <c r="H73" t="n">
-        <v>1.760923977340633</v>
+        <v>2.035280523125299</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J73" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="74">
@@ -3013,21 +3234,24 @@
         <v>72</v>
       </c>
       <c r="E74" t="n">
-        <v>210.3636322021484</v>
+        <v>200.9161071777344</v>
       </c>
       <c r="F74" t="n">
-        <v>272.650146484375</v>
+        <v>288.6792297363281</v>
       </c>
       <c r="G74" t="n">
-        <v>-85.51325225830078</v>
+        <v>-83.09554290771484</v>
       </c>
       <c r="H74" t="n">
-        <v>1.831830929568929</v>
+        <v>1.99518205752952</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J74" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="75">
@@ -3048,21 +3272,24 @@
         <v>73</v>
       </c>
       <c r="E75" t="n">
-        <v>210.296875</v>
+        <v>201.0244445800781</v>
       </c>
       <c r="F75" t="n">
-        <v>273.0823669433594</v>
+        <v>288.615966796875</v>
       </c>
       <c r="G75" t="n">
-        <v>-85.46644592285156</v>
+        <v>-83.05691528320312</v>
       </c>
       <c r="H75" t="n">
-        <v>1.883252345240414</v>
+        <v>1.975468263842481</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J75" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="76">
@@ -3083,21 +3310,24 @@
         <v>74</v>
       </c>
       <c r="E76" t="n">
-        <v>210.2704162597656</v>
+        <v>201.0263671875</v>
       </c>
       <c r="F76" t="n">
-        <v>273.1590270996094</v>
+        <v>288.6145629882812</v>
       </c>
       <c r="G76" t="n">
-        <v>-85.43103790283203</v>
+        <v>-83.0562744140625</v>
       </c>
       <c r="H76" t="n">
-        <v>1.884671224163111</v>
+        <v>1.975074205680053</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J76" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="77">
@@ -3118,21 +3348,24 @@
         <v>75</v>
       </c>
       <c r="E77" t="n">
-        <v>210.1639556884766</v>
+        <v>201.4100189208984</v>
       </c>
       <c r="F77" t="n">
-        <v>273.4580078125</v>
+        <v>288.3769836425781</v>
       </c>
       <c r="G77" t="n">
-        <v>-85.36051940917969</v>
+        <v>-82.94215393066406</v>
       </c>
       <c r="H77" t="n">
-        <v>1.90819770333108</v>
+        <v>1.951987513088365</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J77" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="78">
@@ -3153,21 +3386,24 @@
         <v>76</v>
       </c>
       <c r="E78" t="n">
-        <v>210.1340942382812</v>
+        <v>201.6741027832031</v>
       </c>
       <c r="F78" t="n">
-        <v>273.5326232910156</v>
+        <v>288.2638854980469</v>
       </c>
       <c r="G78" t="n">
-        <v>-85.33585357666016</v>
+        <v>-82.88108062744141</v>
       </c>
       <c r="H78" t="n">
-        <v>1.90721515762367</v>
+        <v>1.97471663368516</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J78" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="79">
@@ -3188,21 +3424,24 @@
         <v>77</v>
       </c>
       <c r="E79" t="n">
-        <v>210.1190948486328</v>
+        <v>201.6890869140625</v>
       </c>
       <c r="F79" t="n">
-        <v>273.5890502929688</v>
+        <v>288.25390625</v>
       </c>
       <c r="G79" t="n">
-        <v>-85.31463623046875</v>
+        <v>-82.87783813476562</v>
       </c>
       <c r="H79" t="n">
-        <v>1.901835290394515</v>
+        <v>1.974249802280984</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J79" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="80">
@@ -3223,21 +3462,24 @@
         <v>78</v>
       </c>
       <c r="E80" t="n">
-        <v>210.1127166748047</v>
+        <v>201.6893310546875</v>
       </c>
       <c r="F80" t="n">
-        <v>273.6133117675781</v>
+        <v>288.2537536621094</v>
       </c>
       <c r="G80" t="n">
-        <v>-85.30652618408203</v>
+        <v>-82.87778472900391</v>
       </c>
       <c r="H80" t="n">
-        <v>1.899878735899931</v>
+        <v>1.974242211526445</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J80" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="81">
@@ -3258,21 +3500,24 @@
         <v>79</v>
       </c>
       <c r="E81" t="n">
-        <v>210.1058807373047</v>
+        <v>202.05224609375</v>
       </c>
       <c r="F81" t="n">
-        <v>273.646728515625</v>
+        <v>287.9949951171875</v>
       </c>
       <c r="G81" t="n">
-        <v>-85.29461669921875</v>
+        <v>-82.89154815673828</v>
       </c>
       <c r="H81" t="n">
-        <v>1.895805955145137</v>
+        <v>1.922556717160382</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J81" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="82">
@@ -3293,21 +3538,24 @@
         <v>80</v>
       </c>
       <c r="E82" t="n">
-        <v>210.0016937255859</v>
+        <v>202.0677185058594</v>
       </c>
       <c r="F82" t="n">
-        <v>273.9674377441406</v>
+        <v>287.9811096191406</v>
       </c>
       <c r="G82" t="n">
-        <v>-85.16120910644531</v>
+        <v>-82.89501953125</v>
       </c>
       <c r="H82" t="n">
-        <v>1.854449705980747</v>
+        <v>1.921333887623168</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J82" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="83">
@@ -3328,21 +3576,24 @@
         <v>81</v>
       </c>
       <c r="E83" t="n">
-        <v>209.9938659667969</v>
+        <v>202.2783508300781</v>
       </c>
       <c r="F83" t="n">
-        <v>274.0039367675781</v>
+        <v>287.7388305664062</v>
       </c>
       <c r="G83" t="n">
-        <v>-85.14382934570312</v>
+        <v>-82.90465545654297</v>
       </c>
       <c r="H83" t="n">
-        <v>1.849851515750964</v>
+        <v>1.88007096440553</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J83" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="84">
@@ -3363,21 +3614,24 @@
         <v>82</v>
       </c>
       <c r="E84" t="n">
-        <v>209.9869232177734</v>
+        <v>202.3196563720703</v>
       </c>
       <c r="F84" t="n">
-        <v>274.0327453613281</v>
+        <v>287.6749572753906</v>
       </c>
       <c r="G84" t="n">
-        <v>-85.12808990478516</v>
+        <v>-82.89846038818359</v>
       </c>
       <c r="H84" t="n">
-        <v>1.845876651404913</v>
+        <v>1.863950002995107</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J84" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="85">
@@ -3398,21 +3652,24 @@
         <v>83</v>
       </c>
       <c r="E85" t="n">
-        <v>209.9011077880859</v>
+        <v>202.3582305908203</v>
       </c>
       <c r="F85" t="n">
-        <v>274.2859191894531</v>
+        <v>287.6167907714844</v>
       </c>
       <c r="G85" t="n">
-        <v>-85.00605010986328</v>
+        <v>-82.88896942138672</v>
       </c>
       <c r="H85" t="n">
-        <v>1.824076037038481</v>
+        <v>1.852061791383693</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J85" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="86">
@@ -3433,21 +3690,24 @@
         <v>84</v>
       </c>
       <c r="E86" t="n">
-        <v>209.8458709716797</v>
+        <v>202.5439147949219</v>
       </c>
       <c r="F86" t="n">
-        <v>274.4748840332031</v>
+        <v>287.337158203125</v>
       </c>
       <c r="G86" t="n">
-        <v>-84.91835784912109</v>
+        <v>-82.81058502197266</v>
       </c>
       <c r="H86" t="n">
-        <v>1.812677597319886</v>
+        <v>1.800145124784066</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J86" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="87">
@@ -3468,21 +3728,24 @@
         <v>85</v>
       </c>
       <c r="E87" t="n">
-        <v>209.8026123046875</v>
+        <v>202.6056823730469</v>
       </c>
       <c r="F87" t="n">
-        <v>274.6001281738281</v>
+        <v>287.224365234375</v>
       </c>
       <c r="G87" t="n">
-        <v>-84.86525726318359</v>
+        <v>-82.77073669433594</v>
       </c>
       <c r="H87" t="n">
-        <v>1.806870281236471</v>
+        <v>1.78813314777718</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J87" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="88">
@@ -3503,21 +3766,24 @@
         <v>86</v>
       </c>
       <c r="E88" t="n">
-        <v>209.7779846191406</v>
+        <v>202.6116180419922</v>
       </c>
       <c r="F88" t="n">
-        <v>274.6622009277344</v>
+        <v>287.2130737304688</v>
       </c>
       <c r="G88" t="n">
-        <v>-84.84060668945312</v>
+        <v>-82.76761627197266</v>
       </c>
       <c r="H88" t="n">
-        <v>1.802945013096648</v>
+        <v>1.786869165824005</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J88" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="89">
@@ -3538,21 +3804,24 @@
         <v>87</v>
       </c>
       <c r="E89" t="n">
-        <v>209.7509613037109</v>
+        <v>202.6559448242188</v>
       </c>
       <c r="F89" t="n">
-        <v>274.7225952148438</v>
+        <v>287.1432800292969</v>
       </c>
       <c r="G89" t="n">
-        <v>-84.82025146484375</v>
+        <v>-82.74938201904297</v>
       </c>
       <c r="H89" t="n">
-        <v>1.797782970717247</v>
+        <v>1.776562515874957</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J89" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="90">
@@ -3573,21 +3842,24 @@
         <v>88</v>
       </c>
       <c r="E90" t="n">
-        <v>209.7354431152344</v>
+        <v>202.6598052978516</v>
       </c>
       <c r="F90" t="n">
-        <v>274.752685546875</v>
+        <v>287.13720703125</v>
       </c>
       <c r="G90" t="n">
-        <v>-84.80763244628906</v>
+        <v>-82.74779510498047</v>
       </c>
       <c r="H90" t="n">
-        <v>1.795289034001228</v>
+        <v>1.775666285444605</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J90" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="91">
@@ -3608,21 +3880,24 @@
         <v>89</v>
       </c>
       <c r="E91" t="n">
-        <v>209.6963806152344</v>
+        <v>202.6976013183594</v>
       </c>
       <c r="F91" t="n">
-        <v>274.8467102050781</v>
+        <v>287.0841979980469</v>
       </c>
       <c r="G91" t="n">
-        <v>-84.77365112304688</v>
+        <v>-82.73151397705078</v>
       </c>
       <c r="H91" t="n">
-        <v>1.783560775356886</v>
+        <v>1.768975049747229</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J91" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="92">
@@ -3643,21 +3918,24 @@
         <v>90</v>
       </c>
       <c r="E92" t="n">
-        <v>209.6363525390625</v>
+        <v>202.6979064941406</v>
       </c>
       <c r="F92" t="n">
-        <v>275.0233764648438</v>
+        <v>287.0837707519531</v>
       </c>
       <c r="G92" t="n">
-        <v>-84.72161102294922</v>
+        <v>-82.73138427734375</v>
       </c>
       <c r="H92" t="n">
-        <v>1.76268720101463</v>
+        <v>1.768921088169024</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J92" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="93">
@@ -3678,21 +3956,24 @@
         <v>91</v>
       </c>
       <c r="E93" t="n">
-        <v>209.6123962402344</v>
+        <v>202.9004364013672</v>
       </c>
       <c r="F93" t="n">
-        <v>275.0901794433594</v>
+        <v>286.7808837890625</v>
       </c>
       <c r="G93" t="n">
-        <v>-84.70541381835938</v>
+        <v>-82.60984802246094</v>
       </c>
       <c r="H93" t="n">
-        <v>1.755118912904121</v>
+        <v>1.748199219676815</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J93" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="94">
@@ -3713,21 +3994,24 @@
         <v>92</v>
       </c>
       <c r="E94" t="n">
-        <v>209.57177734375</v>
+        <v>202.9093170166016</v>
       </c>
       <c r="F94" t="n">
-        <v>275.2115173339844</v>
+        <v>286.7690734863281</v>
       </c>
       <c r="G94" t="n">
-        <v>-84.68244934082031</v>
+        <v>-82.60565948486328</v>
       </c>
       <c r="H94" t="n">
-        <v>1.742619061370241</v>
+        <v>1.748077962524107</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J94" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="95">
@@ -3748,21 +4032,24 @@
         <v>93</v>
       </c>
       <c r="E95" t="n">
-        <v>209.5696563720703</v>
+        <v>202.9417266845703</v>
       </c>
       <c r="F95" t="n">
-        <v>275.2181396484375</v>
+        <v>286.7306213378906</v>
       </c>
       <c r="G95" t="n">
-        <v>-84.68113708496094</v>
+        <v>-82.59437561035156</v>
       </c>
       <c r="H95" t="n">
-        <v>1.742203323580368</v>
+        <v>1.74449443556468</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J95" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="96">
@@ -3783,21 +4070,24 @@
         <v>94</v>
       </c>
       <c r="E96" t="n">
-        <v>209.5610198974609</v>
+        <v>203.0177001953125</v>
       </c>
       <c r="F96" t="n">
-        <v>275.2410278320312</v>
+        <v>286.6014709472656</v>
       </c>
       <c r="G96" t="n">
-        <v>-84.67543792724609</v>
+        <v>-82.55793762207031</v>
       </c>
       <c r="H96" t="n">
-        <v>1.739507201067978</v>
+        <v>1.70992133734471</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J96" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="97">
@@ -3818,21 +4108,24 @@
         <v>95</v>
       </c>
       <c r="E97" t="n">
-        <v>209.5536651611328</v>
+        <v>203.0653839111328</v>
       </c>
       <c r="F97" t="n">
-        <v>275.26513671875</v>
+        <v>286.5244445800781</v>
       </c>
       <c r="G97" t="n">
-        <v>-84.66830444335938</v>
+        <v>-82.54448699951172</v>
       </c>
       <c r="H97" t="n">
-        <v>1.73674900974729</v>
+        <v>1.690691556098484</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J97" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="98">
@@ -3853,21 +4146,24 @@
         <v>96</v>
       </c>
       <c r="E98" t="n">
-        <v>209.5331726074219</v>
+        <v>203.0655822753906</v>
       </c>
       <c r="F98" t="n">
-        <v>275.3306884765625</v>
+        <v>286.5241394042969</v>
       </c>
       <c r="G98" t="n">
-        <v>-84.65169525146484</v>
+        <v>-82.54443359375</v>
       </c>
       <c r="H98" t="n">
-        <v>1.729290774416111</v>
+        <v>1.690614328061351</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J98" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="99">
@@ -3888,21 +4184,24 @@
         <v>97</v>
       </c>
       <c r="E99" t="n">
-        <v>209.4735412597656</v>
+        <v>203.1058654785156</v>
       </c>
       <c r="F99" t="n">
-        <v>275.5589599609375</v>
+        <v>286.4646301269531</v>
       </c>
       <c r="G99" t="n">
-        <v>-84.59857177734375</v>
+        <v>-82.526611328125</v>
       </c>
       <c r="H99" t="n">
-        <v>1.715535193521413</v>
+        <v>1.678099240821854</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J99" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="100">
@@ -3923,21 +4222,24 @@
         <v>98</v>
       </c>
       <c r="E100" t="n">
-        <v>209.4732971191406</v>
+        <v>203.27978515625</v>
       </c>
       <c r="F100" t="n">
-        <v>275.5598754882812</v>
+        <v>286.2572937011719</v>
       </c>
       <c r="G100" t="n">
-        <v>-84.59835815429688</v>
+        <v>-82.52442169189453</v>
       </c>
       <c r="H100" t="n">
-        <v>1.715479950224647</v>
+        <v>1.616379273879065</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J100" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="101">
@@ -3958,21 +4260,24 @@
         <v>99</v>
       </c>
       <c r="E101" t="n">
-        <v>209.4442138671875</v>
+        <v>203.2877655029297</v>
       </c>
       <c r="F101" t="n">
-        <v>275.71142578125</v>
+        <v>286.2463684082031</v>
       </c>
       <c r="G101" t="n">
-        <v>-84.54753875732422</v>
+        <v>-82.52438354492188</v>
       </c>
       <c r="H101" t="n">
-        <v>1.712994907076754</v>
+        <v>1.613577127002016</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J101" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="102">
@@ -3993,21 +4298,24 @@
         <v>100</v>
       </c>
       <c r="E102" t="n">
-        <v>209.4204864501953</v>
+        <v>203.3299713134766</v>
       </c>
       <c r="F102" t="n">
-        <v>275.8222045898438</v>
+        <v>286.1921997070312</v>
       </c>
       <c r="G102" t="n">
-        <v>-84.50548553466797</v>
+        <v>-82.53556060791016</v>
       </c>
       <c r="H102" t="n">
-        <v>1.716563683084248</v>
+        <v>1.594599066310054</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J102" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="103">
@@ -4028,21 +4336,24 @@
         <v>101</v>
       </c>
       <c r="E103" t="n">
-        <v>209.4034881591797</v>
+        <v>203.3301391601562</v>
       </c>
       <c r="F103" t="n">
-        <v>275.9105224609375</v>
+        <v>286.1919860839844</v>
       </c>
       <c r="G103" t="n">
-        <v>-84.47597503662109</v>
+        <v>-82.53560638427734</v>
       </c>
       <c r="H103" t="n">
-        <v>1.720758204929889</v>
+        <v>1.594522849198841</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J103" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="104">
@@ -4063,21 +4374,24 @@
         <v>102</v>
       </c>
       <c r="E104" t="n">
-        <v>209.3651123046875</v>
+        <v>203.4845886230469</v>
       </c>
       <c r="F104" t="n">
-        <v>276.0885620117188</v>
+        <v>286.0169677734375</v>
       </c>
       <c r="G104" t="n">
-        <v>-84.40576171875</v>
+        <v>-82.56052398681641</v>
       </c>
       <c r="H104" t="n">
-        <v>1.73446581131758</v>
+        <v>1.542574867456398</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J104" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="105">
@@ -4098,21 +4412,24 @@
         <v>103</v>
       </c>
       <c r="E105" t="n">
-        <v>209.2914276123047</v>
+        <v>203.4987487792969</v>
       </c>
       <c r="F105" t="n">
-        <v>276.4033813476562</v>
+        <v>286.0009155273438</v>
       </c>
       <c r="G105" t="n">
-        <v>-84.29872131347656</v>
+        <v>-82.56280517578125</v>
       </c>
       <c r="H105" t="n">
-        <v>1.78449027210013</v>
+        <v>1.537811078737659</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J105" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="106">
@@ -4133,21 +4450,24 @@
         <v>104</v>
       </c>
       <c r="E106" t="n">
-        <v>209.2850189208984</v>
+        <v>203.6399841308594</v>
       </c>
       <c r="F106" t="n">
-        <v>276.4480895996094</v>
+        <v>285.8514404296875</v>
       </c>
       <c r="G106" t="n">
-        <v>-84.27906036376953</v>
+        <v>-82.57830047607422</v>
       </c>
       <c r="H106" t="n">
-        <v>1.793082934172488</v>
+        <v>1.516970864182618</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J106" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="107">
@@ -4168,21 +4488,24 @@
         <v>105</v>
       </c>
       <c r="E107" t="n">
-        <v>209.2305450439453</v>
+        <v>203.6405487060547</v>
       </c>
       <c r="F107" t="n">
-        <v>276.7354736328125</v>
+        <v>285.850830078125</v>
       </c>
       <c r="G107" t="n">
-        <v>-84.19091796875</v>
+        <v>-82.57836151123047</v>
       </c>
       <c r="H107" t="n">
-        <v>1.855010771794716</v>
+        <v>1.516887168541834</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J107" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="108">
@@ -4203,21 +4526,24 @@
         <v>106</v>
       </c>
       <c r="E108" t="n">
-        <v>209.1876678466797</v>
+        <v>203.6523895263672</v>
       </c>
       <c r="F108" t="n">
-        <v>276.841064453125</v>
+        <v>285.8390502929688</v>
       </c>
       <c r="G108" t="n">
-        <v>-84.1639404296875</v>
+        <v>-82.57765960693359</v>
       </c>
       <c r="H108" t="n">
-        <v>1.877758936777442</v>
+        <v>1.514562483628613</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J108" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="109">
@@ -4238,21 +4564,24 @@
         <v>107</v>
       </c>
       <c r="E109" t="n">
-        <v>209.1462097167969</v>
+        <v>204.0917205810547</v>
       </c>
       <c r="F109" t="n">
-        <v>276.9721374511719</v>
+        <v>285.3200988769531</v>
       </c>
       <c r="G109" t="n">
-        <v>-84.14337921142578</v>
+        <v>-82.60600280761719</v>
       </c>
       <c r="H109" t="n">
-        <v>1.898548409028886</v>
+        <v>1.497187425122407</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J109" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="110">
@@ -4273,21 +4602,24 @@
         <v>108</v>
       </c>
       <c r="E110" t="n">
-        <v>209.1334533691406</v>
+        <v>204.1722564697266</v>
       </c>
       <c r="F110" t="n">
-        <v>276.9909362792969</v>
+        <v>285.2039794921875</v>
       </c>
       <c r="G110" t="n">
-        <v>-84.13678741455078</v>
+        <v>-82.59111785888672</v>
       </c>
       <c r="H110" t="n">
-        <v>1.895796715302461</v>
+        <v>1.513810867113559</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J110" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="111">
@@ -4308,21 +4640,24 @@
         <v>109</v>
       </c>
       <c r="E111" t="n">
-        <v>209.0536193847656</v>
+        <v>204.1859436035156</v>
       </c>
       <c r="F111" t="n">
-        <v>277.1470336914062</v>
+        <v>285.185302734375</v>
       </c>
       <c r="G111" t="n">
-        <v>-84.06539916992188</v>
+        <v>-82.58838653564453</v>
       </c>
       <c r="H111" t="n">
-        <v>1.865906726620085</v>
+        <v>1.516263704447901</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J111" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="112">
@@ -4343,21 +4678,24 @@
         <v>110</v>
       </c>
       <c r="E112" t="n">
-        <v>208.9834594726562</v>
+        <v>204.4312286376953</v>
       </c>
       <c r="F112" t="n">
-        <v>277.2760009765625</v>
+        <v>284.883056640625</v>
       </c>
       <c r="G112" t="n">
-        <v>-84.01087188720703</v>
+        <v>-82.572265625</v>
       </c>
       <c r="H112" t="n">
-        <v>1.851425911973828</v>
+        <v>1.50971764361027</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J112" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="113">
@@ -4378,21 +4716,24 @@
         <v>111</v>
       </c>
       <c r="E113" t="n">
-        <v>208.9817352294922</v>
+        <v>204.4312896728516</v>
       </c>
       <c r="F113" t="n">
-        <v>277.2791748046875</v>
+        <v>284.8829956054688</v>
       </c>
       <c r="G113" t="n">
-        <v>-84.00952911376953</v>
+        <v>-82.572265625</v>
       </c>
       <c r="H113" t="n">
-        <v>1.851069826367773</v>
+        <v>1.509713597299253</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J113" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="114">
@@ -4413,21 +4754,24 @@
         <v>112</v>
       </c>
       <c r="E114" t="n">
-        <v>208.9611053466797</v>
+        <v>204.4366912841797</v>
       </c>
       <c r="F114" t="n">
-        <v>277.3152770996094</v>
+        <v>284.8782043457031</v>
       </c>
       <c r="G114" t="n">
-        <v>-83.99189758300781</v>
+        <v>-82.57283782958984</v>
       </c>
       <c r="H114" t="n">
-        <v>1.847664992485005</v>
+        <v>1.509123570585069</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J114" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="115">
@@ -4448,21 +4792,24 @@
         <v>113</v>
       </c>
       <c r="E115" t="n">
-        <v>208.9547729492188</v>
+        <v>204.5151519775391</v>
       </c>
       <c r="F115" t="n">
-        <v>277.3259887695312</v>
+        <v>284.7879943847656</v>
       </c>
       <c r="G115" t="n">
-        <v>-83.98615264892578</v>
+        <v>-82.57892608642578</v>
       </c>
       <c r="H115" t="n">
-        <v>1.846419343457939</v>
+        <v>1.493752478078473</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J115" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="116">
@@ -4483,21 +4830,24 @@
         <v>114</v>
       </c>
       <c r="E116" t="n">
-        <v>208.7221374511719</v>
+        <v>204.7325286865234</v>
       </c>
       <c r="F116" t="n">
-        <v>277.789306640625</v>
+        <v>284.5609436035156</v>
       </c>
       <c r="G116" t="n">
-        <v>-83.78475952148438</v>
+        <v>-82.57612609863281</v>
       </c>
       <c r="H116" t="n">
-        <v>1.830754962880665</v>
+        <v>1.478430526946308</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J116" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="117">
@@ -4518,21 +4868,24 @@
         <v>115</v>
       </c>
       <c r="E117" t="n">
-        <v>208.6717987060547</v>
+        <v>204.77392578125</v>
       </c>
       <c r="F117" t="n">
-        <v>277.8536376953125</v>
+        <v>284.5243225097656</v>
       </c>
       <c r="G117" t="n">
-        <v>-83.75735473632812</v>
+        <v>-82.57537841796875</v>
       </c>
       <c r="H117" t="n">
-        <v>1.831937567084175</v>
+        <v>1.47060461641055</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J117" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="118">
@@ -4553,21 +4906,24 @@
         <v>116</v>
       </c>
       <c r="E118" t="n">
-        <v>208.6701354980469</v>
+        <v>204.9363250732422</v>
       </c>
       <c r="F118" t="n">
-        <v>277.8557739257812</v>
+        <v>284.3350219726562</v>
       </c>
       <c r="G118" t="n">
-        <v>-83.75644683837891</v>
+        <v>-82.55508422851562</v>
       </c>
       <c r="H118" t="n">
-        <v>1.83197666143801</v>
+        <v>1.453117865340891</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J118" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="119">
@@ -4588,21 +4944,24 @@
         <v>117</v>
       </c>
       <c r="E119" t="n">
-        <v>208.3179321289062</v>
+        <v>204.9410095214844</v>
       </c>
       <c r="F119" t="n">
-        <v>278.31884765625</v>
+        <v>284.3295593261719</v>
       </c>
       <c r="G119" t="n">
-        <v>-83.63905334472656</v>
+        <v>-82.55449676513672</v>
       </c>
       <c r="H119" t="n">
-        <v>1.878298501857164</v>
+        <v>1.452614131770983</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J119" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="120">
@@ -4623,21 +4982,24 @@
         <v>118</v>
       </c>
       <c r="E120" t="n">
-        <v>208.29052734375</v>
+        <v>205.0136108398438</v>
       </c>
       <c r="F120" t="n">
-        <v>278.3821411132812</v>
+        <v>284.2400207519531</v>
       </c>
       <c r="G120" t="n">
-        <v>-83.63784027099609</v>
+        <v>-82.556396484375</v>
       </c>
       <c r="H120" t="n">
-        <v>1.879968525386624</v>
+        <v>1.448071842020394</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J120" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="121">
@@ -4658,21 +5020,24 @@
         <v>119</v>
       </c>
       <c r="E121" t="n">
-        <v>208.2726898193359</v>
+        <v>205.1926879882812</v>
       </c>
       <c r="F121" t="n">
-        <v>278.4263610839844</v>
+        <v>284.0317687988281</v>
       </c>
       <c r="G121" t="n">
-        <v>-83.63193511962891</v>
+        <v>-82.54473114013672</v>
       </c>
       <c r="H121" t="n">
-        <v>1.881048264782208</v>
+        <v>1.45379382792757</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J121" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="122">
@@ -4693,21 +5058,24 @@
         <v>120</v>
       </c>
       <c r="E122" t="n">
-        <v>208.1441192626953</v>
+        <v>205.2971801757812</v>
       </c>
       <c r="F122" t="n">
-        <v>278.7315673828125</v>
+        <v>283.8529968261719</v>
       </c>
       <c r="G122" t="n">
-        <v>-83.60421752929688</v>
+        <v>-82.54478454589844</v>
       </c>
       <c r="H122" t="n">
-        <v>1.896758355551038</v>
+        <v>1.461350024179935</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J122" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="123">
@@ -4728,21 +5096,24 @@
         <v>121</v>
       </c>
       <c r="E123" t="n">
-        <v>208.0429840087891</v>
+        <v>205.3426666259766</v>
       </c>
       <c r="F123" t="n">
-        <v>279.0267028808594</v>
+        <v>283.7725830078125</v>
       </c>
       <c r="G123" t="n">
-        <v>-83.50640106201172</v>
+        <v>-82.53861236572266</v>
       </c>
       <c r="H123" t="n">
-        <v>1.851034923228186</v>
+        <v>1.467156704759683</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J123" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="124">
@@ -4763,21 +5134,24 @@
         <v>122</v>
       </c>
       <c r="E124" t="n">
-        <v>208.0349884033203</v>
+        <v>205.5390472412109</v>
       </c>
       <c r="F124" t="n">
-        <v>279.0535888671875</v>
+        <v>283.4169616699219</v>
       </c>
       <c r="G124" t="n">
-        <v>-83.49997711181641</v>
+        <v>-82.55926513671875</v>
       </c>
       <c r="H124" t="n">
-        <v>1.845930170251836</v>
+        <v>1.518855033256435</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J124" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="125">
@@ -4798,21 +5172,24 @@
         <v>123</v>
       </c>
       <c r="E125" t="n">
-        <v>208.0255737304688</v>
+        <v>205.5762023925781</v>
       </c>
       <c r="F125" t="n">
-        <v>279.0943908691406</v>
+        <v>283.2734375</v>
       </c>
       <c r="G125" t="n">
-        <v>-83.48699951171875</v>
+        <v>-82.57032012939453</v>
       </c>
       <c r="H125" t="n">
-        <v>1.835251816925032</v>
+        <v>1.524529072862427</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J125" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="126">
@@ -4833,21 +5210,24 @@
         <v>124</v>
       </c>
       <c r="E126" t="n">
-        <v>208.0254211425781</v>
+        <v>205.5783843994141</v>
       </c>
       <c r="F126" t="n">
-        <v>279.0950622558594</v>
+        <v>283.263916015625</v>
       </c>
       <c r="G126" t="n">
-        <v>-83.48678588867188</v>
+        <v>-82.57065582275391</v>
       </c>
       <c r="H126" t="n">
-        <v>1.83507818516362</v>
+        <v>1.524961316593975</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J126" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="127">
@@ -4868,21 +5248,24 @@
         <v>125</v>
       </c>
       <c r="E127" t="n">
-        <v>207.8766174316406</v>
+        <v>205.6633148193359</v>
       </c>
       <c r="F127" t="n">
-        <v>279.4192810058594</v>
+        <v>282.969482421875</v>
       </c>
       <c r="G127" t="n">
-        <v>-83.36452484130859</v>
+        <v>-82.58604431152344</v>
       </c>
       <c r="H127" t="n">
-        <v>1.790879745477173</v>
+        <v>1.54851975214806</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J127" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="128">
@@ -4903,21 +5286,24 @@
         <v>126</v>
       </c>
       <c r="E128" t="n">
-        <v>207.8748168945312</v>
+        <v>205.6679077148438</v>
       </c>
       <c r="F128" t="n">
-        <v>279.4232177734375</v>
+        <v>282.9458618164062</v>
       </c>
       <c r="G128" t="n">
-        <v>-83.363037109375</v>
+        <v>-82.58964538574219</v>
       </c>
       <c r="H128" t="n">
-        <v>1.790342922323087</v>
+        <v>1.550758368518616</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J128" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="129">
@@ -4938,21 +5324,24 @@
         <v>127</v>
       </c>
       <c r="E129" t="n">
-        <v>207.7992248535156</v>
+        <v>205.7158203125</v>
       </c>
       <c r="F129" t="n">
-        <v>279.5997314453125</v>
+        <v>282.8416137695312</v>
       </c>
       <c r="G129" t="n">
-        <v>-83.28841400146484</v>
+        <v>-82.60075378417969</v>
       </c>
       <c r="H129" t="n">
-        <v>1.790527814484553</v>
+        <v>1.55633605874816</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J129" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="130">
@@ -4973,21 +5362,24 @@
         <v>128</v>
       </c>
       <c r="E130" t="n">
-        <v>207.6976470947266</v>
+        <v>205.8366546630859</v>
       </c>
       <c r="F130" t="n">
-        <v>279.7547912597656</v>
+        <v>282.57763671875</v>
       </c>
       <c r="G130" t="n">
-        <v>-83.23095703125</v>
+        <v>-82.64959716796875</v>
       </c>
       <c r="H130" t="n">
-        <v>1.792388813041072</v>
+        <v>1.587444671184399</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J130" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="131">
@@ -5008,21 +5400,24 @@
         <v>129</v>
       </c>
       <c r="E131" t="n">
-        <v>207.5946502685547</v>
+        <v>205.9894104003906</v>
       </c>
       <c r="F131" t="n">
-        <v>279.8844909667969</v>
+        <v>282.3675231933594</v>
       </c>
       <c r="G131" t="n">
-        <v>-83.20377349853516</v>
+        <v>-82.68741607666016</v>
       </c>
       <c r="H131" t="n">
-        <v>1.787689548543289</v>
+        <v>1.605355228305936</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J131" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="132">
@@ -5043,21 +5438,24 @@
         <v>130</v>
       </c>
       <c r="E132" t="n">
-        <v>207.5572967529297</v>
+        <v>206.0919952392578</v>
       </c>
       <c r="F132" t="n">
-        <v>279.9510803222656</v>
+        <v>282.2433166503906</v>
       </c>
       <c r="G132" t="n">
-        <v>-83.19207000732422</v>
+        <v>-82.71247863769531</v>
       </c>
       <c r="H132" t="n">
-        <v>1.781596335624067</v>
+        <v>1.614697079636795</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J132" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="133">
@@ -5078,21 +5476,24 @@
         <v>131</v>
       </c>
       <c r="E133" t="n">
-        <v>207.5562286376953</v>
+        <v>206.1147003173828</v>
       </c>
       <c r="F133" t="n">
-        <v>279.9530639648438</v>
+        <v>282.2149963378906</v>
       </c>
       <c r="G133" t="n">
-        <v>-83.19161224365234</v>
+        <v>-82.71791839599609</v>
       </c>
       <c r="H133" t="n">
-        <v>1.781423389490753</v>
+        <v>1.617437793873383</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J133" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="134">
@@ -5113,21 +5514,24 @@
         <v>132</v>
       </c>
       <c r="E134" t="n">
-        <v>207.3246154785156</v>
+        <v>206.296630859375</v>
       </c>
       <c r="F134" t="n">
-        <v>280.3337707519531</v>
+        <v>282.0107421875</v>
       </c>
       <c r="G134" t="n">
-        <v>-83.12672424316406</v>
+        <v>-82.79389190673828</v>
       </c>
       <c r="H134" t="n">
-        <v>1.776922159354111</v>
+        <v>1.624916487357383</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J134" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="135">
@@ -5148,21 +5552,24 @@
         <v>133</v>
       </c>
       <c r="E135" t="n">
-        <v>207.3063507080078</v>
+        <v>206.3998260498047</v>
       </c>
       <c r="F135" t="n">
-        <v>280.367431640625</v>
+        <v>281.9098205566406</v>
       </c>
       <c r="G135" t="n">
-        <v>-83.12102508544922</v>
+        <v>-82.82163238525391</v>
       </c>
       <c r="H135" t="n">
-        <v>1.773344570873238</v>
+        <v>1.633050026906405</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J135" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="136">
@@ -5183,21 +5590,24 @@
         <v>134</v>
       </c>
       <c r="E136" t="n">
-        <v>207.2584533691406</v>
+        <v>206.4010772705078</v>
       </c>
       <c r="F136" t="n">
-        <v>280.444091796875</v>
+        <v>281.9085998535156</v>
       </c>
       <c r="G136" t="n">
-        <v>-83.10040283203125</v>
+        <v>-82.82196807861328</v>
       </c>
       <c r="H136" t="n">
-        <v>1.75963740084283</v>
+        <v>1.63314881483615</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J136" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="137">
@@ -5218,21 +5628,24 @@
         <v>135</v>
       </c>
       <c r="E137" t="n">
-        <v>207.2523651123047</v>
+        <v>206.4783020019531</v>
       </c>
       <c r="F137" t="n">
-        <v>280.4547424316406</v>
+        <v>281.81884765625</v>
       </c>
       <c r="G137" t="n">
-        <v>-83.09797668457031</v>
+        <v>-82.85330200195312</v>
       </c>
       <c r="H137" t="n">
-        <v>1.757923575995437</v>
+        <v>1.638573290670526</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J137" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="138">
@@ -5253,21 +5666,24 @@
         <v>136</v>
       </c>
       <c r="E138" t="n">
-        <v>207.1865997314453</v>
+        <v>206.5473022460938</v>
       </c>
       <c r="F138" t="n">
-        <v>280.5737609863281</v>
+        <v>281.7213134765625</v>
       </c>
       <c r="G138" t="n">
-        <v>-83.06189727783203</v>
+        <v>-82.88494873046875</v>
       </c>
       <c r="H138" t="n">
-        <v>1.738500954511497</v>
+        <v>1.642059818428737</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J138" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="139">
@@ -5288,21 +5704,24 @@
         <v>137</v>
       </c>
       <c r="E139" t="n">
-        <v>207.1860656738281</v>
+        <v>206.7833251953125</v>
       </c>
       <c r="F139" t="n">
-        <v>280.57470703125</v>
+        <v>281.4208679199219</v>
       </c>
       <c r="G139" t="n">
-        <v>-83.06160736083984</v>
+        <v>-82.94084930419922</v>
       </c>
       <c r="H139" t="n">
-        <v>1.738344320467272</v>
+        <v>1.669823210375025</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J139" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="140">
@@ -5323,21 +5742,24 @@
         <v>138</v>
       </c>
       <c r="E140" t="n">
-        <v>207.1457977294922</v>
+        <v>206.8948974609375</v>
       </c>
       <c r="F140" t="n">
-        <v>280.68212890625</v>
+        <v>281.2186584472656</v>
       </c>
       <c r="G140" t="n">
-        <v>-83.04027557373047</v>
+        <v>-82.97874450683594</v>
       </c>
       <c r="H140" t="n">
-        <v>1.724847681564322</v>
+        <v>1.692973206026649</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J140" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="141">
@@ -5358,21 +5780,24 @@
         <v>139</v>
       </c>
       <c r="E141" t="n">
-        <v>207.1117401123047</v>
+        <v>206.9407043457031</v>
       </c>
       <c r="F141" t="n">
-        <v>280.7931518554688</v>
+        <v>281.154052734375</v>
       </c>
       <c r="G141" t="n">
-        <v>-83.02503204345703</v>
+        <v>-82.98844909667969</v>
       </c>
       <c r="H141" t="n">
-        <v>1.71832680623681</v>
+        <v>1.69934328425863</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J141" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="142">
@@ -5393,21 +5818,24 @@
         <v>140</v>
       </c>
       <c r="E142" t="n">
-        <v>207.1116027832031</v>
+        <v>207.0348815917969</v>
       </c>
       <c r="F142" t="n">
-        <v>280.7936096191406</v>
+        <v>281.0118103027344</v>
       </c>
       <c r="G142" t="n">
-        <v>-83.02497100830078</v>
+        <v>-83.02297973632812</v>
       </c>
       <c r="H142" t="n">
-        <v>1.718300617982483</v>
+        <v>1.700704125420941</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J142" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="143">
@@ -5428,21 +5856,24 @@
         <v>141</v>
       </c>
       <c r="E143" t="n">
-        <v>207.0866851806641</v>
+        <v>207.0369415283203</v>
       </c>
       <c r="F143" t="n">
-        <v>280.8631286621094</v>
+        <v>281.0086364746094</v>
       </c>
       <c r="G143" t="n">
-        <v>-83.01695251464844</v>
+        <v>-83.02356719970703</v>
       </c>
       <c r="H143" t="n">
-        <v>1.714931248651995</v>
+        <v>1.700985081134367</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J143" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="144">
@@ -5463,21 +5894,24 @@
         <v>142</v>
       </c>
       <c r="E144" t="n">
-        <v>207.0864868164062</v>
+        <v>207.1344909667969</v>
       </c>
       <c r="F144" t="n">
-        <v>280.8636779785156</v>
+        <v>280.8515625</v>
       </c>
       <c r="G144" t="n">
-        <v>-83.01689147949219</v>
+        <v>-83.05361175537109</v>
       </c>
       <c r="H144" t="n">
-        <v>1.714904076318685</v>
+        <v>1.714086361336776</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J144" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="145">
@@ -5498,21 +5932,24 @@
         <v>143</v>
       </c>
       <c r="E145" t="n">
-        <v>207.0594024658203</v>
+        <v>207.1350402832031</v>
       </c>
       <c r="F145" t="n">
-        <v>280.9194641113281</v>
+        <v>280.8504943847656</v>
       </c>
       <c r="G145" t="n">
-        <v>-83.01342010498047</v>
+        <v>-83.05391693115234</v>
       </c>
       <c r="H145" t="n">
-        <v>1.710557177215853</v>
+        <v>1.714094700718606</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J145" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="146">
@@ -5533,21 +5970,24 @@
         <v>144</v>
       </c>
       <c r="E146" t="n">
-        <v>206.9407043457031</v>
+        <v>207.3144989013672</v>
       </c>
       <c r="F146" t="n">
-        <v>281.154052734375</v>
+        <v>280.4372863769531</v>
       </c>
       <c r="G146" t="n">
-        <v>-82.98844909667969</v>
+        <v>-83.14257049560547</v>
       </c>
       <c r="H146" t="n">
-        <v>1.69934328425863</v>
+        <v>1.758571803885675</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J146" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="147">
@@ -5568,21 +6008,24 @@
         <v>145</v>
       </c>
       <c r="E147" t="n">
-        <v>206.8948974609375</v>
+        <v>207.3697662353516</v>
       </c>
       <c r="F147" t="n">
-        <v>281.2186584472656</v>
+        <v>280.3581848144531</v>
       </c>
       <c r="G147" t="n">
-        <v>-82.97874450683594</v>
+        <v>-83.14719390869141</v>
       </c>
       <c r="H147" t="n">
-        <v>1.692973206026649</v>
+        <v>1.759830243935289</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J147" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="148">
@@ -5603,21 +6046,24 @@
         <v>146</v>
       </c>
       <c r="E148" t="n">
-        <v>206.7844543457031</v>
+        <v>207.5571899414062</v>
       </c>
       <c r="F148" t="n">
-        <v>281.42236328125</v>
+        <v>279.9585571289062</v>
       </c>
       <c r="G148" t="n">
-        <v>-82.94405364990234</v>
+        <v>-83.19243621826172</v>
       </c>
       <c r="H148" t="n">
-        <v>1.670521592068636</v>
+        <v>1.779924935420324</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J148" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="149">
@@ -5638,21 +6084,24 @@
         <v>147</v>
       </c>
       <c r="E149" t="n">
-        <v>206.5473022460938</v>
+        <v>207.5623626708984</v>
       </c>
       <c r="F149" t="n">
-        <v>281.7213134765625</v>
+        <v>279.9524841308594</v>
       </c>
       <c r="G149" t="n">
-        <v>-82.88494873046875</v>
+        <v>-83.19345855712891</v>
       </c>
       <c r="H149" t="n">
-        <v>1.642059818428737</v>
+        <v>1.780005370346812</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J149" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="150">
@@ -5673,21 +6122,24 @@
         <v>148</v>
       </c>
       <c r="E150" t="n">
-        <v>206.5062408447266</v>
+        <v>207.7069396972656</v>
       </c>
       <c r="F150" t="n">
-        <v>281.7796020507812</v>
+        <v>279.7774963378906</v>
       </c>
       <c r="G150" t="n">
-        <v>-82.86638641357422</v>
+        <v>-83.2371826171875</v>
       </c>
       <c r="H150" t="n">
-        <v>1.639970447693891</v>
+        <v>1.787027553134348</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J150" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="151">
@@ -5708,21 +6160,24 @@
         <v>149</v>
       </c>
       <c r="E151" t="n">
-        <v>206.4740295410156</v>
+        <v>207.7401275634766</v>
       </c>
       <c r="F151" t="n">
-        <v>281.8241577148438</v>
+        <v>279.7332763671875</v>
       </c>
       <c r="G151" t="n">
-        <v>-82.85053253173828</v>
+        <v>-83.24940490722656</v>
       </c>
       <c r="H151" t="n">
-        <v>1.638400139311083</v>
+        <v>1.789252615193512</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J151" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="152">
@@ -5743,21 +6198,24 @@
         <v>150</v>
       </c>
       <c r="E152" t="n">
-        <v>206.4010772705078</v>
+        <v>207.8005828857422</v>
       </c>
       <c r="F152" t="n">
-        <v>281.9085998535156</v>
+        <v>279.6034851074219</v>
       </c>
       <c r="G152" t="n">
-        <v>-82.82196807861328</v>
+        <v>-83.28843688964844</v>
       </c>
       <c r="H152" t="n">
-        <v>1.63314881483615</v>
+        <v>1.790335979950556</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J152" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="153">
@@ -5778,21 +6236,24 @@
         <v>151</v>
       </c>
       <c r="E153" t="n">
-        <v>206.2978820800781</v>
+        <v>207.8165588378906</v>
       </c>
       <c r="F153" t="n">
-        <v>282.009521484375</v>
+        <v>279.5682373046875</v>
       </c>
       <c r="G153" t="n">
-        <v>-82.79422760009766</v>
+        <v>-83.30320739746094</v>
       </c>
       <c r="H153" t="n">
-        <v>1.625015275287128</v>
+        <v>1.788736823897362</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J153" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="154">
@@ -5813,21 +6274,24 @@
         <v>152</v>
       </c>
       <c r="E154" t="n">
-        <v>206.296630859375</v>
+        <v>207.990478515625</v>
       </c>
       <c r="F154" t="n">
-        <v>282.0107421875</v>
+        <v>279.1712036132812</v>
       </c>
       <c r="G154" t="n">
-        <v>-82.79389190673828</v>
+        <v>-83.45807647705078</v>
       </c>
       <c r="H154" t="n">
-        <v>1.624916487357383</v>
+        <v>1.824699604184616</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J154" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="155">
@@ -5848,21 +6312,24 @@
         <v>153</v>
       </c>
       <c r="E155" t="n">
-        <v>206.1147003173828</v>
+        <v>208.028564453125</v>
       </c>
       <c r="F155" t="n">
-        <v>282.2149963378906</v>
+        <v>279.0595092773438</v>
       </c>
       <c r="G155" t="n">
-        <v>-82.71791839599609</v>
+        <v>-83.49678802490234</v>
       </c>
       <c r="H155" t="n">
-        <v>1.617437793873383</v>
+        <v>1.84471121636793</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J155" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="156">
@@ -5883,21 +6350,24 @@
         <v>154</v>
       </c>
       <c r="E156" t="n">
-        <v>206.0919952392578</v>
+        <v>208.04296875</v>
       </c>
       <c r="F156" t="n">
-        <v>282.2433166503906</v>
+        <v>279.0267333984375</v>
       </c>
       <c r="G156" t="n">
-        <v>-82.71247863769531</v>
+        <v>-83.50639343261719</v>
       </c>
       <c r="H156" t="n">
-        <v>1.614697079636795</v>
+        <v>1.851033419861411</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J156" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="157">
@@ -5918,21 +6388,24 @@
         <v>155</v>
       </c>
       <c r="E157" t="n">
-        <v>206.0349578857422</v>
+        <v>208.0782928466797</v>
       </c>
       <c r="F157" t="n">
-        <v>282.3148193359375</v>
+        <v>278.9155578613281</v>
       </c>
       <c r="G157" t="n">
-        <v>-82.70125579833984</v>
+        <v>-83.54729461669922</v>
       </c>
       <c r="H157" t="n">
-        <v>1.609680071338822</v>
+        <v>1.871633695723986</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J157" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="158">
@@ -5953,21 +6426,24 @@
         <v>156</v>
       </c>
       <c r="E158" t="n">
-        <v>206.0073699951172</v>
+        <v>208.1441192626953</v>
       </c>
       <c r="F158" t="n">
-        <v>282.3470764160156</v>
+        <v>278.7315673828125</v>
       </c>
       <c r="G158" t="n">
-        <v>-82.69322967529297</v>
+        <v>-83.60421752929688</v>
       </c>
       <c r="H158" t="n">
-        <v>1.607083115760927</v>
+        <v>1.896758355551038</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J158" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="159">
@@ -5988,21 +6464,24 @@
         <v>157</v>
       </c>
       <c r="E159" t="n">
-        <v>205.9715118408203</v>
+        <v>208.3154296875</v>
       </c>
       <c r="F159" t="n">
-        <v>282.3940734863281</v>
+        <v>278.3832092285156</v>
       </c>
       <c r="G159" t="n">
-        <v>-82.68025970458984</v>
+        <v>-83.64549255371094</v>
       </c>
       <c r="H159" t="n">
-        <v>1.602130345540049</v>
+        <v>1.870284648868137</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J159" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="160">
@@ -6023,21 +6502,24 @@
         <v>158</v>
       </c>
       <c r="E160" t="n">
-        <v>205.8585052490234</v>
+        <v>208.3901824951172</v>
       </c>
       <c r="F160" t="n">
-        <v>282.548828125</v>
+        <v>278.2457885742188</v>
       </c>
       <c r="G160" t="n">
-        <v>-82.65325164794922</v>
+        <v>-83.65272521972656</v>
       </c>
       <c r="H160" t="n">
-        <v>1.589579300503779</v>
+        <v>1.860845637764625</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J160" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="161">
@@ -6058,21 +6540,24 @@
         <v>159</v>
       </c>
       <c r="E161" t="n">
-        <v>205.8473205566406</v>
+        <v>208.4880065917969</v>
       </c>
       <c r="F161" t="n">
-        <v>282.5728454589844</v>
+        <v>278.1160278320312</v>
       </c>
       <c r="G161" t="n">
-        <v>-82.64863586425781</v>
+        <v>-83.68315887451172</v>
       </c>
       <c r="H161" t="n">
-        <v>1.586187424326874</v>
+        <v>1.84761024761184</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J161" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="162">
@@ -6093,21 +6578,24 @@
         <v>160</v>
       </c>
       <c r="E162" t="n">
-        <v>205.8404541015625</v>
+        <v>208.6588592529297</v>
       </c>
       <c r="F162" t="n">
-        <v>282.5878601074219</v>
+        <v>277.8756713867188</v>
       </c>
       <c r="G162" t="n">
-        <v>-82.64699554443359</v>
+        <v>-83.74961853027344</v>
       </c>
       <c r="H162" t="n">
-        <v>1.584086263353398</v>
+        <v>1.832596315952564</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J162" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="163">
@@ -6128,21 +6616,24 @@
         <v>161</v>
       </c>
       <c r="E163" t="n">
-        <v>205.7165069580078</v>
+        <v>208.7221374511719</v>
       </c>
       <c r="F163" t="n">
-        <v>282.8460998535156</v>
+        <v>277.789306640625</v>
       </c>
       <c r="G163" t="n">
-        <v>-82.59969329833984</v>
+        <v>-83.78475952148438</v>
       </c>
       <c r="H163" t="n">
-        <v>1.555550766995733</v>
+        <v>1.830754962880665</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J163" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="164">
@@ -6163,21 +6654,24 @@
         <v>162</v>
       </c>
       <c r="E164" t="n">
-        <v>205.6649017333984</v>
+        <v>208.9547729492188</v>
       </c>
       <c r="F164" t="n">
-        <v>282.9677124023438</v>
+        <v>277.3259887695312</v>
       </c>
       <c r="G164" t="n">
-        <v>-82.58583068847656</v>
+        <v>-83.98615264892578</v>
       </c>
       <c r="H164" t="n">
-        <v>1.548517522799724</v>
+        <v>1.846419343457939</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J164" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="165">
@@ -6198,21 +6692,24 @@
         <v>163</v>
       </c>
       <c r="E165" t="n">
-        <v>205.6416778564453</v>
+        <v>208.9817352294922</v>
       </c>
       <c r="F165" t="n">
-        <v>283.0728149414062</v>
+        <v>277.2791748046875</v>
       </c>
       <c r="G165" t="n">
-        <v>-82.58336639404297</v>
+        <v>-84.00952911376953</v>
       </c>
       <c r="H165" t="n">
-        <v>1.536304190206652</v>
+        <v>1.851069826367773</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J165" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="166">
@@ -6233,21 +6730,24 @@
         <v>164</v>
       </c>
       <c r="E166" t="n">
-        <v>205.5943298339844</v>
+        <v>209.1168212890625</v>
       </c>
       <c r="F166" t="n">
-        <v>283.2162170410156</v>
+        <v>277.0145568847656</v>
       </c>
       <c r="G166" t="n">
-        <v>-82.57387542724609</v>
+        <v>-84.12551116943359</v>
       </c>
       <c r="H166" t="n">
-        <v>1.527718713419982</v>
+        <v>1.889993379253259</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J166" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="167">
@@ -6268,21 +6768,24 @@
         <v>165</v>
       </c>
       <c r="E167" t="n">
-        <v>205.5843505859375</v>
+        <v>209.1251373291016</v>
       </c>
       <c r="F167" t="n">
-        <v>283.2645874023438</v>
+        <v>277.001953125</v>
       </c>
       <c r="G167" t="n">
-        <v>-82.56980895996094</v>
+        <v>-84.13147735595703</v>
       </c>
       <c r="H167" t="n">
-        <v>1.524403219124883</v>
+        <v>1.892935524976979</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J167" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="168">
@@ -6303,21 +6806,24 @@
         <v>166</v>
       </c>
       <c r="E168" t="n">
-        <v>205.5801239013672</v>
+        <v>209.1543121337891</v>
       </c>
       <c r="F168" t="n">
-        <v>283.2841796875</v>
+        <v>276.955322265625</v>
       </c>
       <c r="G168" t="n">
-        <v>-82.56712341308594</v>
+        <v>-84.14360809326172</v>
       </c>
       <c r="H168" t="n">
-        <v>1.523424381273399</v>
+        <v>1.896161986363409</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J168" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="169">
@@ -6338,21 +6844,24 @@
         <v>167</v>
       </c>
       <c r="E169" t="n">
-        <v>205.5390472412109</v>
+        <v>209.1885986328125</v>
       </c>
       <c r="F169" t="n">
-        <v>283.4169616699219</v>
+        <v>276.8408203125</v>
       </c>
       <c r="G169" t="n">
-        <v>-82.55926513671875</v>
+        <v>-84.16324615478516</v>
       </c>
       <c r="H169" t="n">
-        <v>1.518855033256435</v>
+        <v>1.877870897112651</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J169" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="170">
@@ -6373,21 +6882,24 @@
         <v>168</v>
       </c>
       <c r="E170" t="n">
-        <v>205.3895568847656</v>
+        <v>209.2269134521484</v>
       </c>
       <c r="F170" t="n">
-        <v>283.7712097167969</v>
+        <v>276.7413635253906</v>
       </c>
       <c r="G170" t="n">
-        <v>-82.54789733886719</v>
+        <v>-84.19054412841797</v>
       </c>
       <c r="H170" t="n">
-        <v>1.48055761269799</v>
+        <v>1.855984634506881</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J170" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="171">
@@ -6408,21 +6920,24 @@
         <v>169</v>
       </c>
       <c r="E171" t="n">
-        <v>205.2987213134766</v>
+        <v>209.2288360595703</v>
       </c>
       <c r="F171" t="n">
-        <v>283.906005859375</v>
+        <v>276.7325439453125</v>
       </c>
       <c r="G171" t="n">
-        <v>-82.55528259277344</v>
+        <v>-84.19375610351562</v>
       </c>
       <c r="H171" t="n">
-        <v>1.466622181974402</v>
+        <v>1.853796120297833</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J171" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="172">
@@ -6443,21 +6958,24 @@
         <v>170</v>
       </c>
       <c r="E172" t="n">
-        <v>205.2716369628906</v>
+        <v>209.2845306396484</v>
       </c>
       <c r="F172" t="n">
-        <v>283.9478454589844</v>
+        <v>276.4465637207031</v>
       </c>
       <c r="G172" t="n">
-        <v>-82.55441284179688</v>
+        <v>-84.28019714355469</v>
       </c>
       <c r="H172" t="n">
-        <v>1.462810919774812</v>
+        <v>1.792713225159055</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J172" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="173">
@@ -6478,21 +6996,24 @@
         <v>171</v>
       </c>
       <c r="E173" t="n">
-        <v>205.0136108398438</v>
+        <v>209.2857360839844</v>
       </c>
       <c r="F173" t="n">
-        <v>284.2400207519531</v>
+        <v>276.4391784667969</v>
       </c>
       <c r="G173" t="n">
-        <v>-82.556396484375</v>
+        <v>-84.28318786621094</v>
       </c>
       <c r="H173" t="n">
-        <v>1.448071842020394</v>
+        <v>1.791324300771469</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J173" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="174">
@@ -6513,21 +7034,24 @@
         <v>172</v>
       </c>
       <c r="E174" t="n">
-        <v>204.9410095214844</v>
+        <v>209.3189239501953</v>
       </c>
       <c r="F174" t="n">
-        <v>284.3295593261719</v>
+        <v>276.3008422851562</v>
       </c>
       <c r="G174" t="n">
-        <v>-82.55449676513672</v>
+        <v>-84.33901214599609</v>
       </c>
       <c r="H174" t="n">
-        <v>1.452614131770983</v>
+        <v>1.765888395213673</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J174" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="175">
@@ -6548,21 +7072,24 @@
         <v>173</v>
       </c>
       <c r="E175" t="n">
-        <v>204.7344207763672</v>
+        <v>209.3603057861328</v>
       </c>
       <c r="F175" t="n">
-        <v>284.5584716796875</v>
+        <v>276.1106262207031</v>
       </c>
       <c r="G175" t="n">
-        <v>-82.57627868652344</v>
+        <v>-84.39881896972656</v>
       </c>
       <c r="H175" t="n">
-        <v>1.478260470454038</v>
+        <v>1.737733760042774</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J175" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="176">
@@ -6583,21 +7110,24 @@
         <v>174</v>
       </c>
       <c r="E176" t="n">
-        <v>204.6744842529297</v>
+        <v>209.3653411865234</v>
       </c>
       <c r="F176" t="n">
-        <v>284.637939453125</v>
+        <v>276.0711059570312</v>
       </c>
       <c r="G176" t="n">
-        <v>-82.58186340332031</v>
+        <v>-84.41455841064453</v>
       </c>
       <c r="H176" t="n">
-        <v>1.479535440155872</v>
+        <v>1.733071404703048</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J176" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="177">
@@ -6618,21 +7148,24 @@
         <v>175</v>
       </c>
       <c r="E177" t="n">
-        <v>204.4451904296875</v>
+        <v>209.4020233154297</v>
       </c>
       <c r="F177" t="n">
-        <v>284.8705444335938</v>
+        <v>275.9081115722656</v>
       </c>
       <c r="G177" t="n">
-        <v>-82.57425689697266</v>
+        <v>-84.47800445556641</v>
       </c>
       <c r="H177" t="n">
-        <v>1.507887028830303</v>
+        <v>1.720785459128536</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J177" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="178">
@@ -6653,21 +7186,24 @@
         <v>176</v>
       </c>
       <c r="E178" t="n">
-        <v>204.4312286376953</v>
+        <v>209.4220123291016</v>
       </c>
       <c r="F178" t="n">
-        <v>284.883056640625</v>
+        <v>275.832275390625</v>
       </c>
       <c r="G178" t="n">
-        <v>-82.572265625</v>
+        <v>-84.49993896484375</v>
       </c>
       <c r="H178" t="n">
-        <v>1.50971764361027</v>
+        <v>1.716775016357057</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J178" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="179">
@@ -6688,21 +7224,24 @@
         <v>177</v>
       </c>
       <c r="E179" t="n">
-        <v>204.1855316162109</v>
+        <v>209.4732055664062</v>
       </c>
       <c r="F179" t="n">
-        <v>285.1847839355469</v>
+        <v>275.6715698242188</v>
       </c>
       <c r="G179" t="n">
-        <v>-82.58859252929688</v>
+        <v>-84.55301666259766</v>
       </c>
       <c r="H179" t="n">
-        <v>1.516546285135415</v>
+        <v>1.709189963633168</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J179" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="180">
@@ -6723,21 +7262,24 @@
         <v>178</v>
       </c>
       <c r="E180" t="n">
-        <v>204.1849365234375</v>
+        <v>209.490966796875</v>
       </c>
       <c r="F180" t="n">
-        <v>285.1856994628906</v>
+        <v>275.6230773925781</v>
       </c>
       <c r="G180" t="n">
-        <v>-82.58877563476562</v>
+        <v>-84.566162109375</v>
       </c>
       <c r="H180" t="n">
-        <v>1.516427520019573</v>
+        <v>1.708220346563448</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J180" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="181">
@@ -6758,21 +7300,24 @@
         <v>179</v>
       </c>
       <c r="E181" t="n">
-        <v>204.0924682617188</v>
+        <v>209.6091156005859</v>
       </c>
       <c r="F181" t="n">
-        <v>285.3190307617188</v>
+        <v>275.2285766601562</v>
       </c>
       <c r="G181" t="n">
-        <v>-82.60586547851562</v>
+        <v>-84.65023803710938</v>
       </c>
       <c r="H181" t="n">
-        <v>1.497341345881585</v>
+        <v>1.734128308596679</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J181" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="182">
@@ -6793,21 +7338,24 @@
         <v>180</v>
       </c>
       <c r="E182" t="n">
-        <v>204.0917205810547</v>
+        <v>209.6213531494141</v>
       </c>
       <c r="F182" t="n">
-        <v>285.3200988769531</v>
+        <v>275.1920166015625</v>
       </c>
       <c r="G182" t="n">
-        <v>-82.60600280761719</v>
+        <v>-84.66035461425781</v>
       </c>
       <c r="H182" t="n">
-        <v>1.497187425122407</v>
+        <v>1.739475951402407</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J182" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="183">
@@ -6828,21 +7376,24 @@
         <v>181</v>
       </c>
       <c r="E183" t="n">
-        <v>203.6523895263672</v>
+        <v>209.6274261474609</v>
       </c>
       <c r="F183" t="n">
-        <v>285.8390502929688</v>
+        <v>275.1755676269531</v>
       </c>
       <c r="G183" t="n">
-        <v>-82.57765960693359</v>
+        <v>-84.66571807861328</v>
       </c>
       <c r="H183" t="n">
-        <v>1.514562483628613</v>
+        <v>1.741328520236158</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J183" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="184">
@@ -6863,21 +7414,24 @@
         <v>182</v>
       </c>
       <c r="E184" t="n">
-        <v>203.6412658691406</v>
+        <v>209.7312927246094</v>
       </c>
       <c r="F184" t="n">
-        <v>285.8502197265625</v>
+        <v>274.7999267578125</v>
       </c>
       <c r="G184" t="n">
-        <v>-82.57833862304688</v>
+        <v>-84.75978088378906</v>
       </c>
       <c r="H184" t="n">
-        <v>1.516776192161625</v>
+        <v>1.7978555704557</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J184" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="185">
@@ -6898,21 +7452,24 @@
         <v>183</v>
       </c>
       <c r="E185" t="n">
-        <v>203.6411743164062</v>
+        <v>209.7492980957031</v>
       </c>
       <c r="F185" t="n">
-        <v>285.8503112792969</v>
+        <v>274.7466735839844</v>
       </c>
       <c r="G185" t="n">
-        <v>-82.57834625244141</v>
+        <v>-84.78719329833984</v>
       </c>
       <c r="H185" t="n">
-        <v>1.516794044649795</v>
+        <v>1.802746514768844</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J185" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="186">
@@ -6933,21 +7490,24 @@
         <v>184</v>
       </c>
       <c r="E186" t="n">
-        <v>203.2838592529297</v>
+        <v>209.8458709716797</v>
       </c>
       <c r="F186" t="n">
-        <v>286.2524719238281</v>
+        <v>274.4748840332031</v>
       </c>
       <c r="G186" t="n">
-        <v>-82.52259063720703</v>
+        <v>-84.91835784912109</v>
       </c>
       <c r="H186" t="n">
-        <v>1.615261010510079</v>
+        <v>1.812677597319886</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J186" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="187">
@@ -6968,21 +7528,24 @@
         <v>185</v>
       </c>
       <c r="E187" t="n">
-        <v>203.2815856933594</v>
+        <v>209.9848937988281</v>
       </c>
       <c r="F187" t="n">
-        <v>286.2540588378906</v>
+        <v>274.0387268066406</v>
       </c>
       <c r="G187" t="n">
-        <v>-82.52274322509766</v>
+        <v>-85.12519836425781</v>
       </c>
       <c r="H187" t="n">
-        <v>1.616481557346599</v>
+        <v>1.845360660532335</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J187" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="188">
@@ -7003,21 +7566,24 @@
         <v>186</v>
       </c>
       <c r="E188" t="n">
-        <v>203.0655822753906</v>
+        <v>209.9906311035156</v>
       </c>
       <c r="F188" t="n">
-        <v>286.5241394042969</v>
+        <v>274.0189819335938</v>
       </c>
       <c r="G188" t="n">
-        <v>-82.54443359375</v>
+        <v>-85.13665771484375</v>
       </c>
       <c r="H188" t="n">
-        <v>1.690614328061351</v>
+        <v>1.847955087012127</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J188" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="189">
@@ -7038,21 +7604,24 @@
         <v>187</v>
       </c>
       <c r="E189" t="n">
-        <v>202.9476623535156</v>
+        <v>210.0455169677734</v>
       </c>
       <c r="F189" t="n">
-        <v>286.7236633300781</v>
+        <v>273.8475646972656</v>
       </c>
       <c r="G189" t="n">
-        <v>-82.59215545654297</v>
+        <v>-85.22348022460938</v>
       </c>
       <c r="H189" t="n">
-        <v>1.743156147262577</v>
+        <v>1.873853302579885</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J189" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="190">
@@ -7073,21 +7642,24 @@
         <v>188</v>
       </c>
       <c r="E190" t="n">
-        <v>202.9417266845703</v>
+        <v>210.1058807373047</v>
       </c>
       <c r="F190" t="n">
-        <v>286.7306213378906</v>
+        <v>273.646728515625</v>
       </c>
       <c r="G190" t="n">
-        <v>-82.59437561035156</v>
+        <v>-85.29461669921875</v>
       </c>
       <c r="H190" t="n">
-        <v>1.74449443556468</v>
+        <v>1.895805955145137</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J190" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="191">
@@ -7108,21 +7680,24 @@
         <v>189</v>
       </c>
       <c r="E191" t="n">
-        <v>202.9149475097656</v>
+        <v>210.1178436279297</v>
       </c>
       <c r="F191" t="n">
-        <v>286.7649841308594</v>
+        <v>273.5926513671875</v>
       </c>
       <c r="G191" t="n">
-        <v>-82.60205841064453</v>
+        <v>-85.31275939941406</v>
       </c>
       <c r="H191" t="n">
-        <v>1.747668603811855</v>
+        <v>1.901333537261374</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J191" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="192">
@@ -7143,21 +7718,24 @@
         <v>190</v>
       </c>
       <c r="E192" t="n">
-        <v>202.9056396484375</v>
+        <v>210.1340942382812</v>
       </c>
       <c r="F192" t="n">
-        <v>286.779052734375</v>
+        <v>273.5326232910156</v>
       </c>
       <c r="G192" t="n">
-        <v>-82.60597991943359</v>
+        <v>-85.33585357666016</v>
       </c>
       <c r="H192" t="n">
-        <v>1.747628823050791</v>
+        <v>1.90721515762367</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J192" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="193">
@@ -7178,21 +7756,24 @@
         <v>191</v>
       </c>
       <c r="E193" t="n">
-        <v>202.69873046875</v>
+        <v>210.1639556884766</v>
       </c>
       <c r="F193" t="n">
-        <v>287.0825500488281</v>
+        <v>273.4580078125</v>
       </c>
       <c r="G193" t="n">
-        <v>-82.73088073730469</v>
+        <v>-85.36051940917969</v>
       </c>
       <c r="H193" t="n">
-        <v>1.768835919108552</v>
+        <v>1.90819770333108</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J193" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="194">
@@ -7213,21 +7794,24 @@
         <v>192</v>
       </c>
       <c r="E194" t="n">
-        <v>202.6979064941406</v>
+        <v>210.2706604003906</v>
       </c>
       <c r="F194" t="n">
-        <v>287.0837707519531</v>
+        <v>273.1615600585938</v>
       </c>
       <c r="G194" t="n">
-        <v>-82.73138427734375</v>
+        <v>-85.43266296386719</v>
       </c>
       <c r="H194" t="n">
-        <v>1.768921088169024</v>
+        <v>1.885335024525044</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J194" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="195">
@@ -7248,21 +7832,24 @@
         <v>193</v>
       </c>
       <c r="E195" t="n">
-        <v>202.6090698242188</v>
+        <v>210.2772064208984</v>
       </c>
       <c r="F195" t="n">
-        <v>287.2181701660156</v>
+        <v>273.1394958496094</v>
       </c>
       <c r="G195" t="n">
-        <v>-82.76854705810547</v>
+        <v>-85.44015502929688</v>
       </c>
       <c r="H195" t="n">
-        <v>1.787474262962457</v>
+        <v>1.88433538255966</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J195" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="196">
@@ -7283,21 +7870,24 @@
         <v>194</v>
       </c>
       <c r="E196" t="n">
-        <v>202.3282470703125</v>
+        <v>210.2783355712891</v>
       </c>
       <c r="F196" t="n">
-        <v>287.6383972167969</v>
+        <v>273.1348266601562</v>
       </c>
       <c r="G196" t="n">
-        <v>-82.88522338867188</v>
+        <v>-85.44137573242188</v>
       </c>
       <c r="H196" t="n">
-        <v>1.848982569214656</v>
+        <v>1.883999870235776</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J196" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="197">
@@ -7318,21 +7908,24 @@
         <v>195</v>
       </c>
       <c r="E197" t="n">
-        <v>202.0523681640625</v>
+        <v>210.2970428466797</v>
       </c>
       <c r="F197" t="n">
-        <v>287.98974609375</v>
+        <v>273.0611572265625</v>
       </c>
       <c r="G197" t="n">
-        <v>-82.88795471191406</v>
+        <v>-85.45195007324219</v>
       </c>
       <c r="H197" t="n">
-        <v>1.919094999707481</v>
+        <v>1.873032048734752</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J197" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="198">
@@ -7353,21 +7946,24 @@
         <v>196</v>
       </c>
       <c r="E198" t="n">
-        <v>201.7450866699219</v>
+        <v>210.3636627197266</v>
       </c>
       <c r="F198" t="n">
-        <v>288.2262268066406</v>
+        <v>272.6497192382812</v>
       </c>
       <c r="G198" t="n">
-        <v>-82.86749267578125</v>
+        <v>-85.51309967041016</v>
       </c>
       <c r="H198" t="n">
-        <v>1.973063371406893</v>
+        <v>1.831752273125113</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J198" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="199">
@@ -7388,21 +7984,24 @@
         <v>197</v>
       </c>
       <c r="E199" t="n">
-        <v>201.6784210205078</v>
+        <v>210.3634490966797</v>
       </c>
       <c r="F199" t="n">
-        <v>288.2610168457031</v>
+        <v>272.648193359375</v>
       </c>
       <c r="G199" t="n">
-        <v>-82.88014221191406</v>
+        <v>-85.51304626464844</v>
       </c>
       <c r="H199" t="n">
-        <v>1.974581897792085</v>
+        <v>1.831286256344896</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J199" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="200">
@@ -7423,21 +8022,24 @@
         <v>198</v>
       </c>
       <c r="E200" t="n">
-        <v>201.6331787109375</v>
+        <v>210.3519439697266</v>
       </c>
       <c r="F200" t="n">
-        <v>288.28564453125</v>
+        <v>272.5638122558594</v>
       </c>
       <c r="G200" t="n">
-        <v>-82.89496612548828</v>
+        <v>-85.51475524902344</v>
       </c>
       <c r="H200" t="n">
-        <v>1.971310361854731</v>
+        <v>1.803844296018539</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J200" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="201">
@@ -7458,21 +8060,24 @@
         <v>199</v>
       </c>
       <c r="E201" t="n">
-        <v>201.2647247314453</v>
+        <v>210.3518981933594</v>
       </c>
       <c r="F201" t="n">
-        <v>288.5473022460938</v>
+        <v>272.5634765625</v>
       </c>
       <c r="G201" t="n">
-        <v>-82.99076843261719</v>
+        <v>-85.51476287841797</v>
       </c>
       <c r="H201" t="n">
-        <v>1.960711916539746</v>
+        <v>1.80373408734253</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J201" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="202">
@@ -7493,21 +8098,24 @@
         <v>200</v>
       </c>
       <c r="E202" t="n">
-        <v>201.1477813720703</v>
+        <v>210.3376922607422</v>
       </c>
       <c r="F202" t="n">
-        <v>288.6197814941406</v>
+        <v>272.29833984375</v>
       </c>
       <c r="G202" t="n">
-        <v>-83.02555847167969</v>
+        <v>-85.5238037109375</v>
       </c>
       <c r="H202" t="n">
-        <v>1.967801734178023</v>
+        <v>1.728764591403871</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J202" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="203">
@@ -7528,21 +8136,24 @@
         <v>201</v>
       </c>
       <c r="E203" t="n">
-        <v>200.8065032958984</v>
+        <v>210.3093566894531</v>
       </c>
       <c r="F203" t="n">
-        <v>288.7955017089844</v>
+        <v>272.0210571289062</v>
       </c>
       <c r="G203" t="n">
-        <v>-83.143310546875</v>
+        <v>-85.57356262207031</v>
       </c>
       <c r="H203" t="n">
-        <v>2.038351286119363</v>
+        <v>1.663227255313188</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J203" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="204">
@@ -7563,21 +8174,24 @@
         <v>202</v>
       </c>
       <c r="E204" t="n">
-        <v>200.5571899414062</v>
+        <v>210.3467102050781</v>
       </c>
       <c r="F204" t="n">
-        <v>288.9085083007812</v>
+        <v>271.7585754394531</v>
       </c>
       <c r="G204" t="n">
-        <v>-83.23979187011719</v>
+        <v>-85.59589385986328</v>
       </c>
       <c r="H204" t="n">
-        <v>2.112233219934138</v>
+        <v>1.595852032571212</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J204" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="205">
@@ -7598,21 +8212,24 @@
         <v>203</v>
       </c>
       <c r="E205" t="n">
-        <v>200.51806640625</v>
+        <v>210.3742370605469</v>
       </c>
       <c r="F205" t="n">
-        <v>288.9253234863281</v>
+        <v>271.6108093261719</v>
       </c>
       <c r="G205" t="n">
-        <v>-83.25689697265625</v>
+        <v>-85.62557983398438</v>
       </c>
       <c r="H205" t="n">
-        <v>2.1263392244105</v>
+        <v>1.572089430616735</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J205" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="206">
@@ -7633,21 +8250,24 @@
         <v>204</v>
       </c>
       <c r="E206" t="n">
-        <v>200.4172058105469</v>
+        <v>210.3917388916016</v>
       </c>
       <c r="F206" t="n">
-        <v>288.9730529785156</v>
+        <v>271.356201171875</v>
       </c>
       <c r="G206" t="n">
-        <v>-83.28932189941406</v>
+        <v>-85.72994995117188</v>
       </c>
       <c r="H206" t="n">
-        <v>2.155933110714905</v>
+        <v>1.496857253630754</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J206" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="207">
@@ -7668,21 +8288,24 @@
         <v>205</v>
       </c>
       <c r="E207" t="n">
-        <v>200.2453308105469</v>
+        <v>210.4043426513672</v>
       </c>
       <c r="F207" t="n">
-        <v>289.0693054199219</v>
+        <v>271.2779235839844</v>
       </c>
       <c r="G207" t="n">
-        <v>-83.31288909912109</v>
+        <v>-85.775146484375</v>
       </c>
       <c r="H207" t="n">
-        <v>2.189792536459797</v>
+        <v>1.472137899866374</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J207" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="208">
@@ -7703,21 +8326,24 @@
         <v>206</v>
       </c>
       <c r="E208" t="n">
-        <v>200.1328125</v>
+        <v>210.3987274169922</v>
       </c>
       <c r="F208" t="n">
-        <v>289.1033020019531</v>
+        <v>270.8297119140625</v>
       </c>
       <c r="G208" t="n">
-        <v>-83.31496429443359</v>
+        <v>-86.07470703125</v>
       </c>
       <c r="H208" t="n">
-        <v>2.193541928977354</v>
+        <v>1.354860180519526</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J208" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="209">
@@ -7738,21 +8364,24 @@
         <v>207</v>
       </c>
       <c r="E209" t="n">
-        <v>200.0192413330078</v>
+        <v>210.4615173339844</v>
       </c>
       <c r="F209" t="n">
-        <v>289.1424255371094</v>
+        <v>270.4832458496094</v>
       </c>
       <c r="G209" t="n">
-        <v>-83.31983184814453</v>
+        <v>-86.38215637207031</v>
       </c>
       <c r="H209" t="n">
-        <v>2.196801572623156</v>
+        <v>1.332854306648087</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J209" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="210">
@@ -7773,21 +8402,24 @@
         <v>208</v>
       </c>
       <c r="E210" t="n">
-        <v>199.5116729736328</v>
+        <v>210.4646911621094</v>
       </c>
       <c r="F210" t="n">
-        <v>289.3154907226562</v>
+        <v>270.4456481933594</v>
       </c>
       <c r="G210" t="n">
-        <v>-83.47260284423828</v>
+        <v>-86.41306304931641</v>
       </c>
       <c r="H210" t="n">
-        <v>2.186980378135929</v>
+        <v>1.329562305069788</v>
       </c>
       <c r="I210" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J210" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="211">
@@ -7808,21 +8440,24 @@
         <v>209</v>
       </c>
       <c r="E211" t="n">
-        <v>199.2740173339844</v>
+        <v>210.4427032470703</v>
       </c>
       <c r="F211" t="n">
-        <v>289.4104614257812</v>
+        <v>270.2646484375</v>
       </c>
       <c r="G211" t="n">
-        <v>-83.51167297363281</v>
+        <v>-86.72219085693359</v>
       </c>
       <c r="H211" t="n">
-        <v>2.203423686717084</v>
+        <v>1.273058451156498</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J211" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="212">
@@ -7843,21 +8478,24 @@
         <v>210</v>
       </c>
       <c r="E212" t="n">
-        <v>199.1471252441406</v>
+        <v>210.4469757080078</v>
       </c>
       <c r="F212" t="n">
-        <v>289.4486999511719</v>
+        <v>270.1963806152344</v>
       </c>
       <c r="G212" t="n">
-        <v>-83.52263641357422</v>
+        <v>-86.88273620605469</v>
       </c>
       <c r="H212" t="n">
-        <v>2.215865904418526</v>
+        <v>1.254744924174096</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J212" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="213">
@@ -7878,21 +8516,24 @@
         <v>211</v>
       </c>
       <c r="E213" t="n">
-        <v>199.0069732666016</v>
+        <v>210.4461059570312</v>
       </c>
       <c r="F213" t="n">
-        <v>289.4853820800781</v>
+        <v>270.0939636230469</v>
       </c>
       <c r="G213" t="n">
-        <v>-83.51110076904297</v>
+        <v>-87.03681945800781</v>
       </c>
       <c r="H213" t="n">
-        <v>2.224824545557389</v>
+        <v>1.238092977754094</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J213" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="214">
@@ -7913,21 +8554,24 @@
         <v>212</v>
       </c>
       <c r="E214" t="n">
-        <v>198.9833068847656</v>
+        <v>210.4411773681641</v>
       </c>
       <c r="F214" t="n">
-        <v>289.4938659667969</v>
+        <v>270.0675964355469</v>
       </c>
       <c r="G214" t="n">
-        <v>-83.51298522949219</v>
+        <v>-87.09611511230469</v>
       </c>
       <c r="H214" t="n">
-        <v>2.226253581242165</v>
+        <v>1.231320107114696</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J214" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="215">
@@ -7948,21 +8592,24 @@
         <v>213</v>
       </c>
       <c r="E215" t="n">
-        <v>198.5399475097656</v>
+        <v>210.4316253662109</v>
       </c>
       <c r="F215" t="n">
-        <v>289.551025390625</v>
+        <v>269.9737854003906</v>
       </c>
       <c r="G215" t="n">
-        <v>-83.53797912597656</v>
+        <v>-87.36255645751953</v>
       </c>
       <c r="H215" t="n">
-        <v>2.208050879945127</v>
+        <v>1.209045165883061</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J215" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="216">
@@ -7983,21 +8630,24 @@
         <v>214</v>
       </c>
       <c r="E216" t="n">
-        <v>198.5186614990234</v>
+        <v>210.4305725097656</v>
       </c>
       <c r="F216" t="n">
-        <v>289.5521850585938</v>
+        <v>269.9721374511719</v>
       </c>
       <c r="G216" t="n">
-        <v>-83.53986358642578</v>
+        <v>-87.37171173095703</v>
       </c>
       <c r="H216" t="n">
-        <v>2.207773130343951</v>
+        <v>1.208256158048872</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J216" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="217">
@@ -8018,21 +8668,24 @@
         <v>215</v>
       </c>
       <c r="E217" t="n">
-        <v>198.2161865234375</v>
+        <v>210.4181213378906</v>
       </c>
       <c r="F217" t="n">
-        <v>289.5955505371094</v>
+        <v>269.9566040039062</v>
       </c>
       <c r="G217" t="n">
-        <v>-83.56897735595703</v>
+        <v>-87.42236328125</v>
       </c>
       <c r="H217" t="n">
-        <v>2.198075209792124</v>
+        <v>1.200592597562785</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J217" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="218">
@@ -8053,21 +8706,24 @@
         <v>216</v>
       </c>
       <c r="E218" t="n">
-        <v>198.0823211669922</v>
+        <v>210.4021606445312</v>
       </c>
       <c r="F218" t="n">
-        <v>289.6102294921875</v>
+        <v>269.9371337890625</v>
       </c>
       <c r="G218" t="n">
-        <v>-83.59316253662109</v>
+        <v>-87.45785522460938</v>
       </c>
       <c r="H218" t="n">
-        <v>2.191168033087126</v>
+        <v>1.191597464214667</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J218" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="219">
@@ -8088,21 +8744,24 @@
         <v>217</v>
       </c>
       <c r="E219" t="n">
-        <v>198.0468139648438</v>
+        <v>210.3919067382812</v>
       </c>
       <c r="F219" t="n">
-        <v>289.6165161132812</v>
+        <v>269.908935546875</v>
       </c>
       <c r="G219" t="n">
-        <v>-83.60108947753906</v>
+        <v>-87.50183868408203</v>
       </c>
       <c r="H219" t="n">
-        <v>2.188018633795052</v>
+        <v>1.175651291481486</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J219" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="220">
@@ -8123,21 +8782,24 @@
         <v>218</v>
       </c>
       <c r="E220" t="n">
-        <v>197.5897369384766</v>
+        <v>210.2752990722656</v>
       </c>
       <c r="F220" t="n">
-        <v>289.7192077636719</v>
+        <v>269.6709594726562</v>
       </c>
       <c r="G220" t="n">
-        <v>-83.6793212890625</v>
+        <v>-87.82395172119141</v>
       </c>
       <c r="H220" t="n">
-        <v>2.17808412412904</v>
+        <v>1.010066143835194</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J220" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="221">
@@ -8158,21 +8820,24 @@
         <v>219</v>
       </c>
       <c r="E221" t="n">
-        <v>197.5822906494141</v>
+        <v>210.2125854492188</v>
       </c>
       <c r="F221" t="n">
-        <v>289.7212829589844</v>
+        <v>269.5763854980469</v>
       </c>
       <c r="G221" t="n">
-        <v>-83.68022918701172</v>
+        <v>-87.92157745361328</v>
       </c>
       <c r="H221" t="n">
-        <v>2.17821898020381</v>
+        <v>0.9666001359053462</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J221" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="222">
@@ -8193,21 +8858,24 @@
         <v>220</v>
       </c>
       <c r="E222" t="n">
-        <v>197.4184265136719</v>
+        <v>210.1847839355469</v>
       </c>
       <c r="F222" t="n">
-        <v>289.7679138183594</v>
+        <v>269.53857421875</v>
       </c>
       <c r="G222" t="n">
-        <v>-83.70071411132812</v>
+        <v>-87.974365234375</v>
       </c>
       <c r="H222" t="n">
-        <v>2.183857202484166</v>
+        <v>0.955143392066087</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J222" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="223">
@@ -8228,21 +8896,24 @@
         <v>221</v>
       </c>
       <c r="E223" t="n">
-        <v>197.1026000976562</v>
+        <v>210.03759765625</v>
       </c>
       <c r="F223" t="n">
-        <v>289.8453979492188</v>
+        <v>269.2199401855469</v>
       </c>
       <c r="G223" t="n">
-        <v>-83.74785614013672</v>
+        <v>-88.24651336669922</v>
       </c>
       <c r="H223" t="n">
-        <v>2.201992552605664</v>
+        <v>0.8768222709362674</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J223" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="224">
@@ -8263,21 +8934,24 @@
         <v>222</v>
       </c>
       <c r="E224" t="n">
-        <v>196.9754791259766</v>
+        <v>210.0297698974609</v>
       </c>
       <c r="F224" t="n">
-        <v>289.8890686035156</v>
+        <v>269.1992492675781</v>
       </c>
       <c r="G224" t="n">
-        <v>-83.78024291992188</v>
+        <v>-88.25325012207031</v>
       </c>
       <c r="H224" t="n">
-        <v>2.207786711044433</v>
+        <v>0.870745414234479</v>
       </c>
       <c r="I224" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J224" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="225">
@@ -8298,21 +8972,24 @@
         <v>223</v>
       </c>
       <c r="E225" t="n">
-        <v>196.9491882324219</v>
+        <v>209.9115447998047</v>
       </c>
       <c r="F225" t="n">
-        <v>289.9011535644531</v>
+        <v>268.7333984375</v>
       </c>
       <c r="G225" t="n">
-        <v>-83.78666687011719</v>
+        <v>-88.53896331787109</v>
       </c>
       <c r="H225" t="n">
-        <v>2.207947306332783</v>
+        <v>0.8110484300766774</v>
       </c>
       <c r="I225" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J225" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="226">
@@ -8333,21 +9010,24 @@
         <v>224</v>
       </c>
       <c r="E226" t="n">
-        <v>196.9114990234375</v>
+        <v>209.9110565185547</v>
       </c>
       <c r="F226" t="n">
-        <v>289.9224548339844</v>
+        <v>268.7312927246094</v>
       </c>
       <c r="G226" t="n">
-        <v>-83.79945373535156</v>
+        <v>-88.54087829589844</v>
       </c>
       <c r="H226" t="n">
-        <v>2.204765063838464</v>
+        <v>0.8110076293284115</v>
       </c>
       <c r="I226" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J226" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="227">
@@ -8368,21 +9048,24 @@
         <v>225</v>
       </c>
       <c r="E227" t="n">
-        <v>196.9078521728516</v>
+        <v>209.8753204345703</v>
       </c>
       <c r="F227" t="n">
-        <v>289.925048828125</v>
+        <v>268.6541137695312</v>
       </c>
       <c r="G227" t="n">
-        <v>-83.80120849609375</v>
+        <v>-88.58967590332031</v>
       </c>
       <c r="H227" t="n">
-        <v>2.204038653766625</v>
+        <v>0.8061431312661305</v>
       </c>
       <c r="I227" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J227" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="228">
@@ -8403,21 +9086,24 @@
         <v>226</v>
       </c>
       <c r="E228" t="n">
-        <v>196.8161773681641</v>
+        <v>209.8636932373047</v>
       </c>
       <c r="F228" t="n">
-        <v>289.9920959472656</v>
+        <v>268.6072692871094</v>
       </c>
       <c r="G228" t="n">
-        <v>-83.86679840087891</v>
+        <v>-88.61583709716797</v>
       </c>
       <c r="H228" t="n">
-        <v>2.175914843337889</v>
+        <v>0.800056720367015</v>
       </c>
       <c r="I228" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J228" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="229">
@@ -8438,21 +9124,24 @@
         <v>227</v>
       </c>
       <c r="E229" t="n">
-        <v>196.6547698974609</v>
+        <v>209.8212738037109</v>
       </c>
       <c r="F229" t="n">
-        <v>290.0728759765625</v>
+        <v>268.3820190429688</v>
       </c>
       <c r="G229" t="n">
-        <v>-83.87587738037109</v>
+        <v>-88.76286315917969</v>
       </c>
       <c r="H229" t="n">
-        <v>2.166233443233783</v>
+        <v>0.8097347456496192</v>
       </c>
       <c r="I229" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J229" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="230">
@@ -8473,21 +9162,24 @@
         <v>228</v>
       </c>
       <c r="E230" t="n">
-        <v>196.5496368408203</v>
+        <v>209.8215484619141</v>
       </c>
       <c r="F230" t="n">
-        <v>290.0964660644531</v>
+        <v>268.3656921386719</v>
       </c>
       <c r="G230" t="n">
-        <v>-83.89980316162109</v>
+        <v>-88.77684020996094</v>
       </c>
       <c r="H230" t="n">
-        <v>2.137422847962631</v>
+        <v>0.8096494515412184</v>
       </c>
       <c r="I230" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J230" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="231">
@@ -8508,21 +9200,24 @@
         <v>229</v>
       </c>
       <c r="E231" t="n">
-        <v>196.4156799316406</v>
+        <v>209.7842864990234</v>
       </c>
       <c r="F231" t="n">
-        <v>290.121337890625</v>
+        <v>268.2480163574219</v>
       </c>
       <c r="G231" t="n">
-        <v>-83.95188140869141</v>
+        <v>-88.87561798095703</v>
       </c>
       <c r="H231" t="n">
-        <v>2.08661758115641</v>
+        <v>0.7931446916958802</v>
       </c>
       <c r="I231" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J231" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="232">
@@ -8543,21 +9238,24 @@
         <v>230</v>
       </c>
       <c r="E232" t="n">
-        <v>196.4092864990234</v>
+        <v>209.7672271728516</v>
       </c>
       <c r="F232" t="n">
-        <v>290.1234436035156</v>
+        <v>268.2164306640625</v>
       </c>
       <c r="G232" t="n">
-        <v>-83.95395660400391</v>
+        <v>-88.90599060058594</v>
       </c>
       <c r="H232" t="n">
-        <v>2.084125320472519</v>
+        <v>0.7875606688474053</v>
       </c>
       <c r="I232" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J232" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="233">
@@ -8578,21 +9276,24 @@
         <v>231</v>
       </c>
       <c r="E233" t="n">
-        <v>196.1305694580078</v>
+        <v>209.7201995849609</v>
       </c>
       <c r="F233" t="n">
-        <v>290.1968688964844</v>
+        <v>268.0415649414062</v>
       </c>
       <c r="G233" t="n">
-        <v>-83.98780822753906</v>
+        <v>-89.03917694091797</v>
       </c>
       <c r="H233" t="n">
-        <v>2.022574408197916</v>
+        <v>0.7642226124263346</v>
       </c>
       <c r="I233" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J233" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="234">
@@ -8613,21 +9314,24 @@
         <v>232</v>
       </c>
       <c r="E234" t="n">
-        <v>196.1260375976562</v>
+        <v>209.7185211181641</v>
       </c>
       <c r="F234" t="n">
-        <v>290.1980590820312</v>
+        <v>268.0182495117188</v>
       </c>
       <c r="G234" t="n">
-        <v>-83.98835754394531</v>
+        <v>-89.05673217773438</v>
       </c>
       <c r="H234" t="n">
-        <v>2.021573580356052</v>
+        <v>0.7616565471271874</v>
       </c>
       <c r="I234" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J234" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="235">
@@ -8648,21 +9352,24 @@
         <v>233</v>
       </c>
       <c r="E235" t="n">
-        <v>195.7372283935547</v>
+        <v>209.7180938720703</v>
       </c>
       <c r="F235" t="n">
-        <v>290.2706604003906</v>
+        <v>268.01171875</v>
       </c>
       <c r="G235" t="n">
-        <v>-84.04450988769531</v>
+        <v>-89.06202697753906</v>
       </c>
       <c r="H235" t="n">
-        <v>1.976507154445902</v>
+        <v>0.7608853846734245</v>
       </c>
       <c r="I235" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J235" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="236">
@@ -8683,21 +9390,24 @@
         <v>234</v>
       </c>
       <c r="E236" t="n">
-        <v>195.4891967773438</v>
+        <v>209.6598663330078</v>
       </c>
       <c r="F236" t="n">
-        <v>290.3360595703125</v>
+        <v>267.876220703125</v>
       </c>
       <c r="G236" t="n">
-        <v>-84.15049743652344</v>
+        <v>-89.20949554443359</v>
       </c>
       <c r="H236" t="n">
-        <v>1.917475223567121</v>
+        <v>0.7195486608168697</v>
       </c>
       <c r="I236" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J236" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="237">
@@ -8718,21 +9428,24 @@
         <v>235</v>
       </c>
       <c r="E237" t="n">
-        <v>195.4673614501953</v>
+        <v>209.6194000244141</v>
       </c>
       <c r="F237" t="n">
-        <v>290.3399353027344</v>
+        <v>267.8144836425781</v>
       </c>
       <c r="G237" t="n">
-        <v>-84.15322113037109</v>
+        <v>-89.29401397705078</v>
       </c>
       <c r="H237" t="n">
-        <v>1.918414213941109</v>
+        <v>0.7067797732048271</v>
       </c>
       <c r="I237" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J237" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="238">
@@ -8753,21 +9466,24 @@
         <v>236</v>
       </c>
       <c r="E238" t="n">
-        <v>195.3797302246094</v>
+        <v>209.5841217041016</v>
       </c>
       <c r="F238" t="n">
-        <v>290.3554382324219</v>
+        <v>267.6931762695312</v>
       </c>
       <c r="G238" t="n">
-        <v>-84.16936492919922</v>
+        <v>-89.45114135742188</v>
       </c>
       <c r="H238" t="n">
-        <v>1.918575413198445</v>
+        <v>0.6906294343155609</v>
       </c>
       <c r="I238" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J238" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="239">
@@ -8788,21 +9504,24 @@
         <v>237</v>
       </c>
       <c r="E239" t="n">
-        <v>195.3440093994141</v>
+        <v>209.5705413818359</v>
       </c>
       <c r="F239" t="n">
-        <v>290.3603820800781</v>
+        <v>267.6525573730469</v>
       </c>
       <c r="G239" t="n">
-        <v>-84.17974853515625</v>
+        <v>-89.48847961425781</v>
       </c>
       <c r="H239" t="n">
-        <v>1.916295683069226</v>
+        <v>0.6858541005786363</v>
       </c>
       <c r="I239" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J239" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="240">
@@ -8823,21 +9542,24 @@
         <v>238</v>
       </c>
       <c r="E240" t="n">
-        <v>195.3434295654297</v>
+        <v>209.4858703613281</v>
       </c>
       <c r="F240" t="n">
-        <v>290.3604736328125</v>
+        <v>267.530517578125</v>
       </c>
       <c r="G240" t="n">
-        <v>-84.17991638183594</v>
+        <v>-89.58885955810547</v>
       </c>
       <c r="H240" t="n">
-        <v>1.916258614286637</v>
+        <v>0.6640846232746679</v>
       </c>
       <c r="I240" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J240" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="241">
@@ -8858,21 +9580,24 @@
         <v>239</v>
       </c>
       <c r="E241" t="n">
-        <v>195.3303375244141</v>
+        <v>209.4389343261719</v>
       </c>
       <c r="F241" t="n">
-        <v>290.363037109375</v>
+        <v>267.45849609375</v>
       </c>
       <c r="G241" t="n">
-        <v>-84.18431854248047</v>
+        <v>-89.65958404541016</v>
       </c>
       <c r="H241" t="n">
-        <v>1.915438189751437</v>
+        <v>0.6509712926132739</v>
       </c>
       <c r="I241" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J241" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="242">
@@ -8893,21 +9618,24 @@
         <v>240</v>
       </c>
       <c r="E242" t="n">
-        <v>195.2527923583984</v>
+        <v>209.3300170898438</v>
       </c>
       <c r="F242" t="n">
-        <v>290.3755187988281</v>
+        <v>267.2289123535156</v>
       </c>
       <c r="G242" t="n">
-        <v>-84.17261505126953</v>
+        <v>-89.94803619384766</v>
       </c>
       <c r="H242" t="n">
-        <v>1.932902801367226</v>
+        <v>0.6542552907197035</v>
       </c>
       <c r="I242" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J242" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="243">
@@ -8928,21 +9656,24 @@
         <v>241</v>
       </c>
       <c r="E243" t="n">
-        <v>195.0135650634766</v>
+        <v>209.3279724121094</v>
       </c>
       <c r="F243" t="n">
-        <v>290.4068603515625</v>
+        <v>267.1568298339844</v>
       </c>
       <c r="G243" t="n">
-        <v>-84.18479156494141</v>
+        <v>-90.04930114746094</v>
       </c>
       <c r="H243" t="n">
-        <v>1.959236030798022</v>
+        <v>0.6605997599232356</v>
       </c>
       <c r="I243" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J243" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="244">
@@ -8963,21 +9694,24 @@
         <v>242</v>
       </c>
       <c r="E244" t="n">
-        <v>194.9275970458984</v>
+        <v>209.3171844482422</v>
       </c>
       <c r="F244" t="n">
-        <v>290.4239807128906</v>
+        <v>267.0945129394531</v>
       </c>
       <c r="G244" t="n">
-        <v>-84.19379425048828</v>
+        <v>-90.10588073730469</v>
       </c>
       <c r="H244" t="n">
-        <v>1.968776516251827</v>
+        <v>0.6639566009033051</v>
       </c>
       <c r="I244" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J244" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="245">
@@ -8998,21 +9732,24 @@
         <v>243</v>
       </c>
       <c r="E245" t="n">
-        <v>194.8493804931641</v>
+        <v>209.3119506835938</v>
       </c>
       <c r="F245" t="n">
-        <v>290.4183349609375</v>
+        <v>267.0760192871094</v>
       </c>
       <c r="G245" t="n">
-        <v>-84.20437622070312</v>
+        <v>-90.12437438964844</v>
       </c>
       <c r="H245" t="n">
-        <v>1.96617273495885</v>
+        <v>0.6646954716850453</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J245" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="246">
@@ -9033,21 +9770,24 @@
         <v>244</v>
       </c>
       <c r="E246" t="n">
-        <v>194.7582855224609</v>
+        <v>209.2142791748047</v>
       </c>
       <c r="F246" t="n">
-        <v>290.4181213378906</v>
+        <v>266.9383239746094</v>
       </c>
       <c r="G246" t="n">
-        <v>-84.21034240722656</v>
+        <v>-90.27947998046875</v>
       </c>
       <c r="H246" t="n">
-        <v>1.962197572791705</v>
+        <v>0.6649056941283497</v>
       </c>
       <c r="I246" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J246" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="247">
@@ -9068,21 +9808,24 @@
         <v>245</v>
       </c>
       <c r="E247" t="n">
-        <v>194.5998382568359</v>
+        <v>209.1908264160156</v>
       </c>
       <c r="F247" t="n">
-        <v>290.4246826171875</v>
+        <v>266.6869506835938</v>
       </c>
       <c r="G247" t="n">
-        <v>-84.22040557861328</v>
+        <v>-90.49267578125</v>
       </c>
       <c r="H247" t="n">
-        <v>1.95319386823562</v>
+        <v>0.6758048567705207</v>
       </c>
       <c r="I247" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J247" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="248">
@@ -9103,21 +9846,24 @@
         <v>246</v>
       </c>
       <c r="E248" t="n">
-        <v>194.5764923095703</v>
+        <v>209.1067962646484</v>
       </c>
       <c r="F248" t="n">
-        <v>290.427001953125</v>
+        <v>266.5582885742188</v>
       </c>
       <c r="G248" t="n">
-        <v>-84.22103881835938</v>
+        <v>-90.65792846679688</v>
       </c>
       <c r="H248" t="n">
-        <v>1.951915871236064</v>
+        <v>0.6936110521838345</v>
       </c>
       <c r="I248" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J248" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="249">
@@ -9138,21 +9884,24 @@
         <v>247</v>
       </c>
       <c r="E249" t="n">
-        <v>194.4372863769531</v>
+        <v>209.1057891845703</v>
       </c>
       <c r="F249" t="n">
-        <v>290.4705505371094</v>
+        <v>266.5541076660156</v>
       </c>
       <c r="G249" t="n">
-        <v>-84.23857116699219</v>
+        <v>-90.66172027587891</v>
       </c>
       <c r="H249" t="n">
-        <v>1.922737613904351</v>
+        <v>0.6935639285524439</v>
       </c>
       <c r="I249" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J249" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="250">
@@ -9173,21 +9922,24 @@
         <v>248</v>
       </c>
       <c r="E250" t="n">
-        <v>194.0844421386719</v>
+        <v>208.9652252197266</v>
       </c>
       <c r="F250" t="n">
-        <v>290.5565490722656</v>
+        <v>266.2845764160156</v>
       </c>
       <c r="G250" t="n">
-        <v>-84.30989074707031</v>
+        <v>-90.93479156494141</v>
       </c>
       <c r="H250" t="n">
-        <v>1.864387172059141</v>
+        <v>0.6702784357149891</v>
       </c>
       <c r="I250" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J250" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="251">
@@ -9208,21 +9960,24 @@
         <v>249</v>
       </c>
       <c r="E251" t="n">
-        <v>193.9695892333984</v>
+        <v>208.9464263916016</v>
       </c>
       <c r="F251" t="n">
-        <v>290.6227722167969</v>
+        <v>266.2120666503906</v>
       </c>
       <c r="G251" t="n">
-        <v>-84.34337615966797</v>
+        <v>-90.984619140625</v>
       </c>
       <c r="H251" t="n">
-        <v>1.830523936929804</v>
+        <v>0.6789129081882471</v>
       </c>
       <c r="I251" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J251" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="252">
@@ -9243,21 +9998,24 @@
         <v>250</v>
       </c>
       <c r="E252" t="n">
-        <v>193.9325103759766</v>
+        <v>208.8929443359375</v>
       </c>
       <c r="F252" t="n">
-        <v>290.6415100097656</v>
+        <v>266.1228332519531</v>
       </c>
       <c r="G252" t="n">
-        <v>-84.34896850585938</v>
+        <v>-91.04353332519531</v>
       </c>
       <c r="H252" t="n">
-        <v>1.820874366390041</v>
+        <v>0.6797310391203149</v>
       </c>
       <c r="I252" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J252" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="253">
@@ -9278,21 +10036,24 @@
         <v>251</v>
       </c>
       <c r="E253" t="n">
-        <v>193.6699523925781</v>
+        <v>208.8171539306641</v>
       </c>
       <c r="F253" t="n">
-        <v>290.7580261230469</v>
+        <v>265.8172912597656</v>
       </c>
       <c r="G253" t="n">
-        <v>-84.42745208740234</v>
+        <v>-91.30950164794922</v>
       </c>
       <c r="H253" t="n">
-        <v>1.748758165624278</v>
+        <v>0.6687280444462347</v>
       </c>
       <c r="I253" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J253" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="254">
@@ -9313,21 +10074,24 @@
         <v>252</v>
       </c>
       <c r="E254" t="n">
-        <v>193.4266052246094</v>
+        <v>208.8221435546875</v>
       </c>
       <c r="F254" t="n">
-        <v>290.9247131347656</v>
+        <v>265.7714538574219</v>
       </c>
       <c r="G254" t="n">
-        <v>-84.49999237060547</v>
+        <v>-91.35726928710938</v>
       </c>
       <c r="H254" t="n">
-        <v>1.672573979571431</v>
+        <v>0.6764401364956902</v>
       </c>
       <c r="I254" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J254" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="255">
@@ -9348,21 +10112,24 @@
         <v>253</v>
       </c>
       <c r="E255" t="n">
-        <v>193.3864288330078</v>
+        <v>208.8162078857422</v>
       </c>
       <c r="F255" t="n">
-        <v>290.9471435546875</v>
+        <v>265.7447509765625</v>
       </c>
       <c r="G255" t="n">
-        <v>-84.51610565185547</v>
+        <v>-91.39031982421875</v>
       </c>
       <c r="H255" t="n">
-        <v>1.659016876275512</v>
+        <v>0.6740838025034306</v>
       </c>
       <c r="I255" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J255" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="256">
@@ -9383,21 +10150,24 @@
         <v>254</v>
       </c>
       <c r="E256" t="n">
-        <v>193.3251953125</v>
+        <v>208.7839965820312</v>
       </c>
       <c r="F256" t="n">
-        <v>290.9883422851562</v>
+        <v>265.6678466796875</v>
       </c>
       <c r="G256" t="n">
-        <v>-84.54135131835938</v>
+        <v>-91.4910888671875</v>
       </c>
       <c r="H256" t="n">
-        <v>1.634117431824627</v>
+        <v>0.6693832295287536</v>
       </c>
       <c r="I256" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J256" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="257">
@@ -9418,21 +10188,24 @@
         <v>255</v>
       </c>
       <c r="E257" t="n">
-        <v>193.2339630126953</v>
+        <v>208.7816772460938</v>
       </c>
       <c r="F257" t="n">
-        <v>291.0610656738281</v>
+        <v>265.4978942871094</v>
       </c>
       <c r="G257" t="n">
-        <v>-84.57854461669922</v>
+        <v>-91.67790222167969</v>
       </c>
       <c r="H257" t="n">
-        <v>1.592921308891097</v>
+        <v>0.6757981954075157</v>
       </c>
       <c r="I257" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J257" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="258">
@@ -9453,21 +10226,24 @@
         <v>256</v>
       </c>
       <c r="E258" t="n">
-        <v>193.2335968017578</v>
+        <v>208.781005859375</v>
       </c>
       <c r="F258" t="n">
-        <v>291.0613708496094</v>
+        <v>265.4946899414062</v>
       </c>
       <c r="G258" t="n">
-        <v>-84.57869720458984</v>
+        <v>-91.68141174316406</v>
       </c>
       <c r="H258" t="n">
-        <v>1.592755862614255</v>
+        <v>0.6763012663534126</v>
       </c>
       <c r="I258" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J258" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="259">
@@ -9488,21 +10264,24 @@
         <v>257</v>
       </c>
       <c r="E259" t="n">
-        <v>193.126708984375</v>
+        <v>208.6889190673828</v>
       </c>
       <c r="F259" t="n">
-        <v>291.1252746582031</v>
+        <v>265.3486022949219</v>
       </c>
       <c r="G259" t="n">
-        <v>-84.6121826171875</v>
+        <v>-91.88065338134766</v>
       </c>
       <c r="H259" t="n">
-        <v>1.549829821945417</v>
+        <v>0.6923086577354375</v>
       </c>
       <c r="I259" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J259" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="260">
@@ -9523,21 +10302,24 @@
         <v>258</v>
       </c>
       <c r="E260" t="n">
-        <v>193.1262817382812</v>
+        <v>208.6851196289062</v>
       </c>
       <c r="F260" t="n">
-        <v>291.1255187988281</v>
+        <v>265.3287658691406</v>
       </c>
       <c r="G260" t="n">
-        <v>-84.61231994628906</v>
+        <v>-91.90060424804688</v>
       </c>
       <c r="H260" t="n">
-        <v>1.549657428207792</v>
+        <v>0.6926495884442661</v>
       </c>
       <c r="I260" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J260" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="261">
@@ -9558,21 +10340,24 @@
         <v>259</v>
       </c>
       <c r="E261" t="n">
-        <v>192.9014129638672</v>
+        <v>208.6851043701172</v>
       </c>
       <c r="F261" t="n">
-        <v>291.2795715332031</v>
+        <v>265.3286743164062</v>
       </c>
       <c r="G261" t="n">
-        <v>-84.72597503662109</v>
+        <v>-91.90068817138672</v>
       </c>
       <c r="H261" t="n">
-        <v>1.479885304384955</v>
+        <v>0.6926509576438998</v>
       </c>
       <c r="I261" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J261" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="262">
@@ -9593,21 +10378,24 @@
         <v>260</v>
       </c>
       <c r="E262" t="n">
-        <v>192.8701019287109</v>
+        <v>208.5661010742188</v>
       </c>
       <c r="F262" t="n">
-        <v>291.2966003417969</v>
+        <v>265.1545104980469</v>
       </c>
       <c r="G262" t="n">
-        <v>-84.73902130126953</v>
+        <v>-92.10530853271484</v>
       </c>
       <c r="H262" t="n">
-        <v>1.471544043776309</v>
+        <v>0.6808871629125992</v>
       </c>
       <c r="I262" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J262" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="263">
@@ -9628,21 +10416,24 @@
         <v>261</v>
       </c>
       <c r="E263" t="n">
-        <v>192.6564331054688</v>
+        <v>208.5620269775391</v>
       </c>
       <c r="F263" t="n">
-        <v>291.4046020507812</v>
+        <v>265.1450805664062</v>
       </c>
       <c r="G263" t="n">
-        <v>-84.78018188476562</v>
+        <v>-92.11399078369141</v>
       </c>
       <c r="H263" t="n">
-        <v>1.406654868045639</v>
+        <v>0.6813708960117256</v>
       </c>
       <c r="I263" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J263" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="264">
@@ -9663,21 +10454,24 @@
         <v>262</v>
       </c>
       <c r="E264" t="n">
-        <v>192.6529541015625</v>
+        <v>208.56201171875</v>
       </c>
       <c r="F264" t="n">
-        <v>291.4063720703125</v>
+        <v>265.1450500488281</v>
       </c>
       <c r="G264" t="n">
-        <v>-84.78085327148438</v>
+        <v>-92.11402893066406</v>
       </c>
       <c r="H264" t="n">
-        <v>1.405599759497173</v>
+        <v>0.6813728387149349</v>
       </c>
       <c r="I264" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J264" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="265">
@@ -9698,21 +10492,24 @@
         <v>263</v>
       </c>
       <c r="E265" t="n">
-        <v>192.5669860839844</v>
+        <v>208.5410308837891</v>
       </c>
       <c r="F265" t="n">
-        <v>291.4619140625</v>
+        <v>265.0799560546875</v>
       </c>
       <c r="G265" t="n">
-        <v>-84.78898620605469</v>
+        <v>-92.16258239746094</v>
       </c>
       <c r="H265" t="n">
-        <v>1.381459252610397</v>
+        <v>0.6823304231338193</v>
       </c>
       <c r="I265" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J265" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="266">
@@ -9733,21 +10530,24 @@
         <v>264</v>
       </c>
       <c r="E266" t="n">
-        <v>192.5068969726562</v>
+        <v>208.5301208496094</v>
       </c>
       <c r="F266" t="n">
-        <v>291.5044555664062</v>
+        <v>265.0634155273438</v>
       </c>
       <c r="G266" t="n">
-        <v>-84.80634307861328</v>
+        <v>-92.17635345458984</v>
       </c>
       <c r="H266" t="n">
-        <v>1.363198290923009</v>
+        <v>0.679214061164775</v>
       </c>
       <c r="I266" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J266" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="267">
@@ -9768,21 +10568,24 @@
         <v>265</v>
       </c>
       <c r="E267" t="n">
-        <v>192.3642730712891</v>
+        <v>208.5124206542969</v>
       </c>
       <c r="F267" t="n">
-        <v>291.5740051269531</v>
+        <v>265.0127258300781</v>
       </c>
       <c r="G267" t="n">
-        <v>-84.83557891845703</v>
+        <v>-92.21111297607422</v>
       </c>
       <c r="H267" t="n">
-        <v>1.324283272587083</v>
+        <v>0.6645159398338392</v>
       </c>
       <c r="I267" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J267" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="268">
@@ -9803,21 +10606,24 @@
         <v>266</v>
       </c>
       <c r="E268" t="n">
-        <v>192.214111328125</v>
+        <v>208.4194641113281</v>
       </c>
       <c r="F268" t="n">
-        <v>291.6047058105469</v>
+        <v>264.8051147460938</v>
       </c>
       <c r="G268" t="n">
-        <v>-84.84787750244141</v>
+        <v>-92.35696411132812</v>
       </c>
       <c r="H268" t="n">
-        <v>1.283754568087751</v>
+        <v>0.6504696579685438</v>
       </c>
       <c r="I268" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J268" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="269">
@@ -9838,21 +10644,24 @@
         <v>267</v>
       </c>
       <c r="E269" t="n">
-        <v>192.1788024902344</v>
+        <v>208.4190063476562</v>
       </c>
       <c r="F269" t="n">
-        <v>291.613037109375</v>
+        <v>264.8024291992188</v>
       </c>
       <c r="G269" t="n">
-        <v>-84.84727478027344</v>
+        <v>-92.35890960693359</v>
       </c>
       <c r="H269" t="n">
-        <v>1.274968670801505</v>
+        <v>0.6503067890861475</v>
       </c>
       <c r="I269" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J269" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="270">
@@ -9873,21 +10682,24 @@
         <v>268</v>
       </c>
       <c r="E270" t="n">
-        <v>191.7744445800781</v>
+        <v>208.3580017089844</v>
       </c>
       <c r="F270" t="n">
-        <v>291.6683349609375</v>
+        <v>264.668701171875</v>
       </c>
       <c r="G270" t="n">
-        <v>-84.8048095703125</v>
+        <v>-92.46588134765625</v>
       </c>
       <c r="H270" t="n">
-        <v>1.19104016203132</v>
+        <v>0.630707829664357</v>
       </c>
       <c r="I270" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J270" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="271">
@@ -9908,21 +10720,24 @@
         <v>269</v>
       </c>
       <c r="E271" t="n">
-        <v>191.5382995605469</v>
+        <v>208.3575134277344</v>
       </c>
       <c r="F271" t="n">
-        <v>291.6726989746094</v>
+        <v>264.6676330566406</v>
       </c>
       <c r="G271" t="n">
-        <v>-84.72673034667969</v>
+        <v>-92.46674346923828</v>
       </c>
       <c r="H271" t="n">
-        <v>1.15479292274216</v>
+        <v>0.6305497735399876</v>
       </c>
       <c r="I271" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J271" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="272">
@@ -9943,21 +10758,24 @@
         <v>270</v>
       </c>
       <c r="E272" t="n">
-        <v>191.4961700439453</v>
+        <v>208.3076171875</v>
       </c>
       <c r="F272" t="n">
-        <v>291.6736145019531</v>
+        <v>264.6033020019531</v>
       </c>
       <c r="G272" t="n">
-        <v>-84.72219848632812</v>
+        <v>-92.51667022705078</v>
       </c>
       <c r="H272" t="n">
-        <v>1.145731115106568</v>
+        <v>0.6236101823168683</v>
       </c>
       <c r="I272" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J272" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="273">
@@ -9978,21 +10796,24 @@
         <v>271</v>
       </c>
       <c r="E273" t="n">
-        <v>191.4253845214844</v>
+        <v>208.3070068359375</v>
       </c>
       <c r="F273" t="n">
-        <v>291.675048828125</v>
+        <v>264.6025085449219</v>
       </c>
       <c r="G273" t="n">
-        <v>-84.7093505859375</v>
+        <v>-92.51727294921875</v>
       </c>
       <c r="H273" t="n">
-        <v>1.134132716356238</v>
+        <v>0.623525895783794</v>
       </c>
       <c r="I273" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J273" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="274">
@@ -10013,21 +10834,24 @@
         <v>272</v>
       </c>
       <c r="E274" t="n">
-        <v>191.4007110595703</v>
+        <v>208.2085418701172</v>
       </c>
       <c r="F274" t="n">
-        <v>291.6713256835938</v>
+        <v>264.372802734375</v>
       </c>
       <c r="G274" t="n">
-        <v>-84.70635986328125</v>
+        <v>-92.71347808837891</v>
       </c>
       <c r="H274" t="n">
-        <v>1.127322891056491</v>
+        <v>0.6309921148150179</v>
       </c>
       <c r="I274" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J274" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="275">
@@ -10048,21 +10872,24 @@
         <v>273</v>
       </c>
       <c r="E275" t="n">
-        <v>191.1896820068359</v>
+        <v>208.1839904785156</v>
       </c>
       <c r="F275" t="n">
-        <v>291.6728515625</v>
+        <v>264.3253784179688</v>
       </c>
       <c r="G275" t="n">
-        <v>-84.67117309570312</v>
+        <v>-92.74243927001953</v>
       </c>
       <c r="H275" t="n">
-        <v>1.059442526923382</v>
+        <v>0.6425560524418767</v>
       </c>
       <c r="I275" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J275" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="276">
@@ -10083,21 +10910,24 @@
         <v>274</v>
       </c>
       <c r="E276" t="n">
-        <v>191.1033172607422</v>
+        <v>208.1465606689453</v>
       </c>
       <c r="F276" t="n">
-        <v>291.6527099609375</v>
+        <v>264.2896118164062</v>
       </c>
       <c r="G276" t="n">
-        <v>-84.66790771484375</v>
+        <v>-92.76580810546875</v>
       </c>
       <c r="H276" t="n">
-        <v>1.021866076227498</v>
+        <v>0.6424309610407941</v>
       </c>
       <c r="I276" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J276" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="277">
@@ -10118,21 +10948,24 @@
         <v>275</v>
       </c>
       <c r="E277" t="n">
-        <v>190.7872467041016</v>
+        <v>208.1461029052734</v>
       </c>
       <c r="F277" t="n">
-        <v>291.6189270019531</v>
+        <v>264.2891845703125</v>
       </c>
       <c r="G277" t="n">
-        <v>-84.61802673339844</v>
+        <v>-92.76609039306641</v>
       </c>
       <c r="H277" t="n">
-        <v>0.8900423852777946</v>
+        <v>0.642429441712036</v>
       </c>
       <c r="I277" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J277" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="278">
@@ -10153,21 +10986,24 @@
         <v>276</v>
       </c>
       <c r="E278" t="n">
-        <v>190.6886138916016</v>
+        <v>208.0520782470703</v>
       </c>
       <c r="F278" t="n">
-        <v>291.5989379882812</v>
+        <v>264.1116943359375</v>
       </c>
       <c r="G278" t="n">
-        <v>-84.63288879394531</v>
+        <v>-92.85561370849609</v>
       </c>
       <c r="H278" t="n">
-        <v>0.8433991042441424</v>
+        <v>0.642583425837507</v>
       </c>
       <c r="I278" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J278" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="279">
@@ -10188,21 +11024,24 @@
         <v>277</v>
       </c>
       <c r="E279" t="n">
-        <v>190.6161651611328</v>
+        <v>207.9892578125</v>
       </c>
       <c r="F279" t="n">
-        <v>291.5975341796875</v>
+        <v>263.9239807128906</v>
       </c>
       <c r="G279" t="n">
-        <v>-84.63631439208984</v>
+        <v>-93.01251983642578</v>
       </c>
       <c r="H279" t="n">
-        <v>0.8150705591102292</v>
+        <v>0.6690004658526879</v>
       </c>
       <c r="I279" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J279" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="280">
@@ -10223,21 +11062,24 @@
         <v>278</v>
       </c>
       <c r="E280" t="n">
-        <v>190.2993774414062</v>
+        <v>207.9944610595703</v>
       </c>
       <c r="F280" t="n">
-        <v>291.5710144042969</v>
+        <v>263.8892211914062</v>
       </c>
       <c r="G280" t="n">
-        <v>-84.63328552246094</v>
+        <v>-93.03458404541016</v>
       </c>
       <c r="H280" t="n">
-        <v>0.6933893728884992</v>
+        <v>0.6619103637585171</v>
       </c>
       <c r="I280" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J280" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="281">
@@ -10258,21 +11100,24 @@
         <v>279</v>
       </c>
       <c r="E281" t="n">
-        <v>189.8874664306641</v>
+        <v>208.0002288818359</v>
       </c>
       <c r="F281" t="n">
-        <v>291.5507202148438</v>
+        <v>263.8824157714844</v>
       </c>
       <c r="G281" t="n">
-        <v>-84.64100646972656</v>
+        <v>-93.05374145507812</v>
       </c>
       <c r="H281" t="n">
-        <v>0.5611754206135837</v>
+        <v>0.6467354252878443</v>
       </c>
       <c r="I281" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
+      </c>
+      <c r="J281" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="282">
@@ -10293,231 +11138,24 @@
         <v>280</v>
       </c>
       <c r="E282" t="n">
-        <v>189.7459259033203</v>
+        <v>208.0319366455078</v>
       </c>
       <c r="F282" t="n">
-        <v>291.6015930175781</v>
+        <v>263.7550964355469</v>
       </c>
       <c r="G282" t="n">
-        <v>-84.61186981201172</v>
+        <v>-93.68702697753906</v>
       </c>
       <c r="H282" t="n">
-        <v>0.5092622999808987</v>
+        <v>0.6467354252878443</v>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>Standard</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="n">
-        <v>2</v>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>LCA</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>LCA_B07</t>
-        </is>
-      </c>
-      <c r="D283" t="n">
-        <v>281</v>
-      </c>
-      <c r="E283" t="n">
-        <v>189.4462280273438</v>
-      </c>
-      <c r="F283" t="n">
-        <v>291.5890197753906</v>
-      </c>
-      <c r="G283" t="n">
-        <v>-84.59609222412109</v>
-      </c>
-      <c r="H283" t="n">
-        <v>0.4102223282871231</v>
-      </c>
-      <c r="I283" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="n">
-        <v>2</v>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>LCA</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>LCA_B07</t>
-        </is>
-      </c>
-      <c r="D284" t="n">
-        <v>282</v>
-      </c>
-      <c r="E284" t="n">
-        <v>189.4073638916016</v>
-      </c>
-      <c r="F284" t="n">
-        <v>291.5984802246094</v>
-      </c>
-      <c r="G284" t="n">
-        <v>-84.57352447509766</v>
-      </c>
-      <c r="H284" t="n">
-        <v>0.391923582856894</v>
-      </c>
-      <c r="I284" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="n">
-        <v>2</v>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>LCA</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>LCA_B07</t>
-        </is>
-      </c>
-      <c r="D285" t="n">
-        <v>283</v>
-      </c>
-      <c r="E285" t="n">
-        <v>189.4068908691406</v>
-      </c>
-      <c r="F285" t="n">
-        <v>291.5986022949219</v>
-      </c>
-      <c r="G285" t="n">
-        <v>-84.57324981689453</v>
-      </c>
-      <c r="H285" t="n">
-        <v>0.3917013308881058</v>
-      </c>
-      <c r="I285" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="n">
-        <v>2</v>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>LCA</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>LCA_B07</t>
-        </is>
-      </c>
-      <c r="D286" t="n">
-        <v>284</v>
-      </c>
-      <c r="E286" t="n">
-        <v>189.3373107910156</v>
-      </c>
-      <c r="F286" t="n">
-        <v>291.6297607421875</v>
-      </c>
-      <c r="G286" t="n">
-        <v>-84.54961395263672</v>
-      </c>
-      <c r="H286" t="n">
-        <v>0.3602426343396315</v>
-      </c>
-      <c r="I286" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="n">
-        <v>2</v>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>LCA</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>LCA_B07</t>
-        </is>
-      </c>
-      <c r="D287" t="n">
-        <v>285</v>
-      </c>
-      <c r="E287" t="n">
-        <v>189.3370361328125</v>
-      </c>
-      <c r="F287" t="n">
-        <v>291.6298828125</v>
-      </c>
-      <c r="G287" t="n">
-        <v>-84.54952239990234</v>
-      </c>
-      <c r="H287" t="n">
-        <v>0.3601162941928505</v>
-      </c>
-      <c r="I287" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="n">
-        <v>2</v>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>LCA</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>LCA_B07</t>
-        </is>
-      </c>
-      <c r="D288" t="n">
-        <v>286</v>
-      </c>
-      <c r="E288" t="n">
-        <v>189.0160675048828</v>
-      </c>
-      <c r="F288" t="n">
-        <v>291.7065124511719</v>
-      </c>
-      <c r="G288" t="n">
-        <v>-84.40533447265625</v>
-      </c>
-      <c r="H288" t="n">
-        <v>0.3601162941928505</v>
-      </c>
-      <c r="I288" t="inlineStr">
-        <is>
           <t>Endpoint</t>
         </is>
+      </c>
+      <c r="J282" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
